--- a/automation/reports/excel/Passed_Test_Cases.xlsx
+++ b/automation/reports/excel/Passed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="1026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="1030">
   <si>
     <t>Test ID</t>
   </si>
@@ -286,12 +286,18 @@
     <t>Authentication Verification - Case 40</t>
   </si>
   <si>
+    <t>TC_AZ_001</t>
+  </si>
+  <si>
+    <t>Authorization</t>
+  </si>
+  <si>
+    <t>Authorization Verification - Case 1</t>
+  </si>
+  <si>
     <t>TC_AZ_002</t>
   </si>
   <si>
-    <t>Authorization</t>
-  </si>
-  <si>
     <t>Authorization Verification - Case 2</t>
   </si>
   <si>
@@ -391,6 +397,12 @@
     <t>Authorization Verification - Case 18</t>
   </si>
   <si>
+    <t>TC_AZ_019</t>
+  </si>
+  <si>
+    <t>Authorization Verification - Case 19</t>
+  </si>
+  <si>
     <t>TC_AZ_020</t>
   </si>
   <si>
@@ -472,6 +484,12 @@
     <t>Registration Verification - Case 2</t>
   </si>
   <si>
+    <t>TC_REG_003</t>
+  </si>
+  <si>
+    <t>Registration Verification - Case 3</t>
+  </si>
+  <si>
     <t>TC_REG_004</t>
   </si>
   <si>
@@ -661,6 +679,12 @@
     <t>Profile Management Verification - Case 14</t>
   </si>
   <si>
+    <t>TC_PROF_015</t>
+  </si>
+  <si>
+    <t>Profile Management Verification - Case 15</t>
+  </si>
+  <si>
     <t>TC_PROF_016</t>
   </si>
   <si>
@@ -712,18 +736,6 @@
     <t>Navigation Verification - Case 3</t>
   </si>
   <si>
-    <t>TC_NAV_004</t>
-  </si>
-  <si>
-    <t>Navigation Verification - Case 4</t>
-  </si>
-  <si>
-    <t>TC_NAV_005</t>
-  </si>
-  <si>
-    <t>Navigation Verification - Case 5</t>
-  </si>
-  <si>
     <t>TC_NAV_006</t>
   </si>
   <si>
@@ -931,12 +943,6 @@
     <t>Dashboard Verification - Case 9</t>
   </si>
   <si>
-    <t>TC_DASH_010</t>
-  </si>
-  <si>
-    <t>Dashboard Verification - Case 10</t>
-  </si>
-  <si>
     <t>TC_DASH_011</t>
   </si>
   <si>
@@ -1042,12 +1048,6 @@
     <t>Forms Verification - Case 7</t>
   </si>
   <si>
-    <t>TC_FORM_008</t>
-  </si>
-  <si>
-    <t>Forms Verification - Case 8</t>
-  </si>
-  <si>
     <t>TC_FORM_009</t>
   </si>
   <si>
@@ -1351,12 +1351,6 @@
     <t>CRUD Operations Verification - Case 18</t>
   </si>
   <si>
-    <t>TC_CRUD_019</t>
-  </si>
-  <si>
-    <t>CRUD Operations Verification - Case 19</t>
-  </si>
-  <si>
     <t>TC_CRUD_020</t>
   </si>
   <si>
@@ -1405,6 +1399,12 @@
     <t>CRUD Operations Verification - Case 27</t>
   </si>
   <si>
+    <t>TC_CRUD_028</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 28</t>
+  </si>
+  <si>
     <t>TC_CRUD_029</t>
   </si>
   <si>
@@ -1504,12 +1504,6 @@
     <t>Search Verification - Case 4</t>
   </si>
   <si>
-    <t>TC_SRCH_005</t>
-  </si>
-  <si>
-    <t>Search Verification - Case 5</t>
-  </si>
-  <si>
     <t>TC_SRCH_006</t>
   </si>
   <si>
@@ -1657,12 +1651,6 @@
     <t>Filters Verification - Case 9</t>
   </si>
   <si>
-    <t>TC_FILT_010</t>
-  </si>
-  <si>
-    <t>Filters Verification - Case 10</t>
-  </si>
-  <si>
     <t>TC_FILT_011</t>
   </si>
   <si>
@@ -1681,6 +1669,12 @@
     <t>Filters Verification - Case 13</t>
   </si>
   <si>
+    <t>TC_FILT_014</t>
+  </si>
+  <si>
+    <t>Filters Verification - Case 14</t>
+  </si>
+  <si>
     <t>TC_FILT_015</t>
   </si>
   <si>
@@ -1726,6 +1720,12 @@
     <t>Input Validation Verification - Case 1</t>
   </si>
   <si>
+    <t>TC_VAL_002</t>
+  </si>
+  <si>
+    <t>Input Validation Verification - Case 2</t>
+  </si>
+  <si>
     <t>TC_VAL_003</t>
   </si>
   <si>
@@ -2005,12 +2005,6 @@
     <t>Error Handling Verification - Case 8</t>
   </si>
   <si>
-    <t>TC_ERR_009</t>
-  </si>
-  <si>
-    <t>Error Handling Verification - Case 9</t>
-  </si>
-  <si>
     <t>TC_ERR_010</t>
   </si>
   <si>
@@ -2176,12 +2170,6 @@
     <t>Session Management Verification - Case 16</t>
   </si>
   <si>
-    <t>TC_SESS_017</t>
-  </si>
-  <si>
-    <t>Session Management Verification - Case 17</t>
-  </si>
-  <si>
     <t>TC_SESS_018</t>
   </si>
   <si>
@@ -2287,6 +2275,12 @@
     <t>Notifications Verification - Case 14</t>
   </si>
   <si>
+    <t>TC_NOTIF_015</t>
+  </si>
+  <si>
+    <t>Notifications Verification - Case 15</t>
+  </si>
+  <si>
     <t>TC_NOTIF_016</t>
   </si>
   <si>
@@ -2422,12 +2416,6 @@
     <t>File Upload Verification - Case 17</t>
   </si>
   <si>
-    <t>TC_UPL_018</t>
-  </si>
-  <si>
-    <t>File Upload Verification - Case 18</t>
-  </si>
-  <si>
     <t>TC_UPL_019</t>
   </si>
   <si>
@@ -2503,12 +2491,18 @@
     <t>Offline Handling Verification - Case 10</t>
   </si>
   <si>
+    <t>TC_ACC_001</t>
+  </si>
+  <si>
+    <t>Accessibility</t>
+  </si>
+  <si>
+    <t>Accessibility Verification - Case 1</t>
+  </si>
+  <si>
     <t>TC_ACC_002</t>
   </si>
   <si>
-    <t>Accessibility</t>
-  </si>
-  <si>
     <t>Accessibility Verification - Case 2</t>
   </si>
   <si>
@@ -2671,6 +2665,12 @@
     <t>Responsive UI Verification - Case 8</t>
   </si>
   <si>
+    <t>TC_RESP_009</t>
+  </si>
+  <si>
+    <t>Responsive UI Verification - Case 9</t>
+  </si>
+  <si>
     <t>TC_RESP_010</t>
   </si>
   <si>
@@ -2800,12 +2800,18 @@
     <t>Performance Smoke Tests Verification - Case 20</t>
   </si>
   <si>
+    <t>TC_REGR_001</t>
+  </si>
+  <si>
+    <t>Regression Suite</t>
+  </si>
+  <si>
+    <t>Regression Suite Verification - Case 1</t>
+  </si>
+  <si>
     <t>TC_REGR_002</t>
   </si>
   <si>
-    <t>Regression Suite</t>
-  </si>
-  <si>
     <t>Regression Suite Verification - Case 2</t>
   </si>
   <si>
@@ -2879,6 +2885,12 @@
   </si>
   <si>
     <t>Regression Suite Verification - Case 14</t>
+  </si>
+  <si>
+    <t>TC_REGR_015</t>
+  </si>
+  <si>
+    <t>Regression Suite Verification - Case 15</t>
   </si>
   <si>
     <t>TC_REGR_016</t>
@@ -3479,7 +3491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F499"/>
+  <dimension ref="A1:F501"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3526,7 +3538,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>220</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3546,7 +3558,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>168</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3566,7 +3578,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>285</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3586,7 +3598,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>127</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3606,7 +3618,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>284</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3626,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3646,7 +3658,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>263</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3666,7 +3678,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>233</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3686,7 +3698,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>289</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3706,7 +3718,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <v>106</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3726,7 +3738,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>178</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3746,7 +3758,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>182</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3766,7 +3778,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>187</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -3786,7 +3798,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>158</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -3806,7 +3818,7 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>119</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -3826,7 +3838,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>142</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3846,7 +3858,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>254</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3866,7 +3878,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>166</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3886,7 +3898,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>262</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3906,7 +3918,7 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>243</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3926,7 +3938,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>209</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3946,7 +3958,7 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>197</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -3966,7 +3978,7 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>242</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -3986,7 +3998,7 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>120</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -4006,7 +4018,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>242</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -4026,7 +4038,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>212</v>
+        <v>265</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -4046,7 +4058,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>225</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -4066,7 +4078,7 @@
         <v>10</v>
       </c>
       <c r="F29">
-        <v>161</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -4086,7 +4098,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>200</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -4106,7 +4118,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>249</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -4126,7 +4138,7 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>101</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -4146,7 +4158,7 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>245</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -4166,7 +4178,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>284</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -4186,7 +4198,7 @@
         <v>10</v>
       </c>
       <c r="F35">
-        <v>195</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4206,7 +4218,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>293</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -4226,7 +4238,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>208</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -4246,7 +4258,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>222</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -4266,7 +4278,7 @@
         <v>10</v>
       </c>
       <c r="F39">
-        <v>153</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -4286,7 +4298,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -4306,7 +4318,7 @@
         <v>10</v>
       </c>
       <c r="F41">
-        <v>207</v>
+        <v>264</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -4320,13 +4332,13 @@
         <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
       </c>
       <c r="F42">
-        <v>202</v>
+        <v>249</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -4340,13 +4352,13 @@
         <v>95</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
         <v>10</v>
       </c>
       <c r="F43">
-        <v>168</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -4360,13 +4372,13 @@
         <v>97</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
       </c>
       <c r="F44">
-        <v>284</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -4380,13 +4392,13 @@
         <v>99</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
       </c>
       <c r="F45">
-        <v>145</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -4400,13 +4412,13 @@
         <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
       </c>
       <c r="F46">
-        <v>250</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -4420,13 +4432,13 @@
         <v>103</v>
       </c>
       <c r="D47" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
       </c>
       <c r="F47">
-        <v>263</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -4440,13 +4452,13 @@
         <v>105</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
       </c>
       <c r="F48">
-        <v>202</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -4460,13 +4472,13 @@
         <v>107</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
       </c>
       <c r="F49">
-        <v>280</v>
+        <v>186</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -4480,13 +4492,13 @@
         <v>109</v>
       </c>
       <c r="D50" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E50" t="s">
         <v>10</v>
       </c>
       <c r="F50">
-        <v>294</v>
+        <v>258</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4500,13 +4512,13 @@
         <v>111</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
       </c>
       <c r="F51">
-        <v>233</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4520,13 +4532,13 @@
         <v>113</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
       </c>
       <c r="F52">
-        <v>109</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4540,13 +4552,13 @@
         <v>115</v>
       </c>
       <c r="D53" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
       </c>
       <c r="F53">
-        <v>163</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -4560,13 +4572,13 @@
         <v>117</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
       </c>
       <c r="F54">
-        <v>216</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4580,13 +4592,13 @@
         <v>119</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E55" t="s">
         <v>10</v>
       </c>
       <c r="F55">
-        <v>145</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4600,13 +4612,13 @@
         <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
       </c>
       <c r="F56">
-        <v>169</v>
+        <v>230</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4620,13 +4632,13 @@
         <v>123</v>
       </c>
       <c r="D57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
       </c>
       <c r="F57">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -4640,13 +4652,13 @@
         <v>125</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
       </c>
       <c r="F58">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -4660,13 +4672,13 @@
         <v>127</v>
       </c>
       <c r="D59" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
       </c>
       <c r="F59">
-        <v>264</v>
+        <v>254</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -4680,13 +4692,13 @@
         <v>129</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
       </c>
       <c r="F60">
-        <v>248</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -4700,13 +4712,13 @@
         <v>131</v>
       </c>
       <c r="D61" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
       </c>
       <c r="F61">
-        <v>181</v>
+        <v>251</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -4720,13 +4732,13 @@
         <v>133</v>
       </c>
       <c r="D62" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
       </c>
       <c r="F62">
-        <v>114</v>
+        <v>231</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -4740,13 +4752,13 @@
         <v>135</v>
       </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
       </c>
       <c r="F63">
-        <v>250</v>
+        <v>191</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -4760,13 +4772,13 @@
         <v>137</v>
       </c>
       <c r="D64" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
       </c>
       <c r="F64">
-        <v>121</v>
+        <v>280</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -4780,13 +4792,13 @@
         <v>139</v>
       </c>
       <c r="D65" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
       </c>
       <c r="F65">
-        <v>217</v>
+        <v>187</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4800,13 +4812,13 @@
         <v>141</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
       </c>
       <c r="F66">
-        <v>247</v>
+        <v>285</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -4820,13 +4832,13 @@
         <v>143</v>
       </c>
       <c r="D67" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
       </c>
       <c r="F67">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4840,13 +4852,13 @@
         <v>145</v>
       </c>
       <c r="D68" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
       </c>
       <c r="F68">
-        <v>224</v>
+        <v>171</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -4860,13 +4872,13 @@
         <v>147</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
       </c>
       <c r="F69">
-        <v>201</v>
+        <v>160</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -4874,47 +4886,47 @@
         <v>148</v>
       </c>
       <c r="B70" t="s">
+        <v>92</v>
+      </c>
+      <c r="C70" t="s">
         <v>149</v>
       </c>
-      <c r="C70" t="s">
-        <v>150</v>
-      </c>
       <c r="D70" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
       </c>
       <c r="F70">
-        <v>269</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>150</v>
+      </c>
+      <c r="B71" t="s">
+        <v>92</v>
+      </c>
+      <c r="C71" t="s">
         <v>151</v>
       </c>
-      <c r="B71" t="s">
-        <v>149</v>
-      </c>
-      <c r="C71" t="s">
-        <v>152</v>
-      </c>
       <c r="D71" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
       </c>
       <c r="F71">
-        <v>214</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>152</v>
+      </c>
+      <c r="B72" t="s">
         <v>153</v>
-      </c>
-      <c r="B72" t="s">
-        <v>149</v>
       </c>
       <c r="C72" t="s">
         <v>154</v>
@@ -4926,7 +4938,7 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>255</v>
+        <v>193</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4934,7 +4946,7 @@
         <v>155</v>
       </c>
       <c r="B73" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C73" t="s">
         <v>156</v>
@@ -4946,7 +4958,7 @@
         <v>10</v>
       </c>
       <c r="F73">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -4954,7 +4966,7 @@
         <v>157</v>
       </c>
       <c r="B74" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C74" t="s">
         <v>158</v>
@@ -4966,7 +4978,7 @@
         <v>10</v>
       </c>
       <c r="F74">
-        <v>157</v>
+        <v>216</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -4974,7 +4986,7 @@
         <v>159</v>
       </c>
       <c r="B75" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C75" t="s">
         <v>160</v>
@@ -4986,7 +4998,7 @@
         <v>10</v>
       </c>
       <c r="F75">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -4994,7 +5006,7 @@
         <v>161</v>
       </c>
       <c r="B76" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C76" t="s">
         <v>162</v>
@@ -5006,7 +5018,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>199</v>
+        <v>299</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -5014,7 +5026,7 @@
         <v>163</v>
       </c>
       <c r="B77" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C77" t="s">
         <v>164</v>
@@ -5026,7 +5038,7 @@
         <v>10</v>
       </c>
       <c r="F77">
-        <v>229</v>
+        <v>159</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -5034,7 +5046,7 @@
         <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C78" t="s">
         <v>166</v>
@@ -5046,7 +5058,7 @@
         <v>10</v>
       </c>
       <c r="F78">
-        <v>117</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -5054,7 +5066,7 @@
         <v>167</v>
       </c>
       <c r="B79" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C79" t="s">
         <v>168</v>
@@ -5066,7 +5078,7 @@
         <v>10</v>
       </c>
       <c r="F79">
-        <v>237</v>
+        <v>271</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -5074,7 +5086,7 @@
         <v>169</v>
       </c>
       <c r="B80" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C80" t="s">
         <v>170</v>
@@ -5086,7 +5098,7 @@
         <v>10</v>
       </c>
       <c r="F80">
-        <v>136</v>
+        <v>268</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -5094,7 +5106,7 @@
         <v>171</v>
       </c>
       <c r="B81" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C81" t="s">
         <v>172</v>
@@ -5106,7 +5118,7 @@
         <v>10</v>
       </c>
       <c r="F81">
-        <v>213</v>
+        <v>142</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -5114,7 +5126,7 @@
         <v>173</v>
       </c>
       <c r="B82" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C82" t="s">
         <v>174</v>
@@ -5126,7 +5138,7 @@
         <v>10</v>
       </c>
       <c r="F82">
-        <v>222</v>
+        <v>296</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -5134,7 +5146,7 @@
         <v>175</v>
       </c>
       <c r="B83" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C83" t="s">
         <v>176</v>
@@ -5146,7 +5158,7 @@
         <v>10</v>
       </c>
       <c r="F83">
-        <v>180</v>
+        <v>238</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -5154,7 +5166,7 @@
         <v>177</v>
       </c>
       <c r="B84" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C84" t="s">
         <v>178</v>
@@ -5166,7 +5178,7 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>280</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -5174,7 +5186,7 @@
         <v>179</v>
       </c>
       <c r="B85" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C85" t="s">
         <v>180</v>
@@ -5186,7 +5198,7 @@
         <v>10</v>
       </c>
       <c r="F85">
-        <v>226</v>
+        <v>181</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -5194,7 +5206,7 @@
         <v>181</v>
       </c>
       <c r="B86" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C86" t="s">
         <v>182</v>
@@ -5206,7 +5218,7 @@
         <v>10</v>
       </c>
       <c r="F86">
-        <v>110</v>
+        <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -5214,7 +5226,7 @@
         <v>183</v>
       </c>
       <c r="B87" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C87" t="s">
         <v>184</v>
@@ -5226,7 +5238,7 @@
         <v>10</v>
       </c>
       <c r="F87">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -5234,7 +5246,7 @@
         <v>185</v>
       </c>
       <c r="B88" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C88" t="s">
         <v>186</v>
@@ -5246,7 +5258,7 @@
         <v>10</v>
       </c>
       <c r="F88">
-        <v>280</v>
+        <v>267</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -5254,67 +5266,67 @@
         <v>187</v>
       </c>
       <c r="B89" t="s">
+        <v>153</v>
+      </c>
+      <c r="C89" t="s">
         <v>188</v>
       </c>
-      <c r="C89" t="s">
-        <v>189</v>
-      </c>
       <c r="D89" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
       </c>
       <c r="F89">
-        <v>213</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>189</v>
+      </c>
+      <c r="B90" t="s">
+        <v>153</v>
+      </c>
+      <c r="C90" t="s">
         <v>190</v>
       </c>
-      <c r="B90" t="s">
-        <v>188</v>
-      </c>
-      <c r="C90" t="s">
-        <v>191</v>
-      </c>
       <c r="D90" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
       </c>
       <c r="F90">
-        <v>131</v>
+        <v>166</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>191</v>
+      </c>
+      <c r="B91" t="s">
+        <v>153</v>
+      </c>
+      <c r="C91" t="s">
         <v>192</v>
       </c>
-      <c r="B91" t="s">
-        <v>188</v>
-      </c>
-      <c r="C91" t="s">
-        <v>193</v>
-      </c>
       <c r="D91" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E91" t="s">
         <v>10</v>
       </c>
       <c r="F91">
-        <v>223</v>
+        <v>204</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>193</v>
+      </c>
+      <c r="B92" t="s">
         <v>194</v>
-      </c>
-      <c r="B92" t="s">
-        <v>188</v>
       </c>
       <c r="C92" t="s">
         <v>195</v>
@@ -5326,7 +5338,7 @@
         <v>10</v>
       </c>
       <c r="F92">
-        <v>180</v>
+        <v>146</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -5334,7 +5346,7 @@
         <v>196</v>
       </c>
       <c r="B93" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C93" t="s">
         <v>197</v>
@@ -5346,7 +5358,7 @@
         <v>10</v>
       </c>
       <c r="F93">
-        <v>239</v>
+        <v>250</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -5354,7 +5366,7 @@
         <v>198</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C94" t="s">
         <v>199</v>
@@ -5366,7 +5378,7 @@
         <v>10</v>
       </c>
       <c r="F94">
-        <v>106</v>
+        <v>226</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -5374,7 +5386,7 @@
         <v>200</v>
       </c>
       <c r="B95" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C95" t="s">
         <v>201</v>
@@ -5386,7 +5398,7 @@
         <v>10</v>
       </c>
       <c r="F95">
-        <v>125</v>
+        <v>165</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -5394,7 +5406,7 @@
         <v>202</v>
       </c>
       <c r="B96" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C96" t="s">
         <v>203</v>
@@ -5406,7 +5418,7 @@
         <v>10</v>
       </c>
       <c r="F96">
-        <v>119</v>
+        <v>196</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -5414,7 +5426,7 @@
         <v>204</v>
       </c>
       <c r="B97" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C97" t="s">
         <v>205</v>
@@ -5426,7 +5438,7 @@
         <v>10</v>
       </c>
       <c r="F97">
-        <v>213</v>
+        <v>126</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -5434,7 +5446,7 @@
         <v>206</v>
       </c>
       <c r="B98" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C98" t="s">
         <v>207</v>
@@ -5446,7 +5458,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>268</v>
+        <v>143</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -5454,7 +5466,7 @@
         <v>208</v>
       </c>
       <c r="B99" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C99" t="s">
         <v>209</v>
@@ -5466,7 +5478,7 @@
         <v>10</v>
       </c>
       <c r="F99">
-        <v>270</v>
+        <v>296</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -5474,7 +5486,7 @@
         <v>210</v>
       </c>
       <c r="B100" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C100" t="s">
         <v>211</v>
@@ -5486,7 +5498,7 @@
         <v>10</v>
       </c>
       <c r="F100">
-        <v>219</v>
+        <v>245</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -5494,7 +5506,7 @@
         <v>212</v>
       </c>
       <c r="B101" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C101" t="s">
         <v>213</v>
@@ -5506,7 +5518,7 @@
         <v>10</v>
       </c>
       <c r="F101">
-        <v>188</v>
+        <v>113</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -5514,7 +5526,7 @@
         <v>214</v>
       </c>
       <c r="B102" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C102" t="s">
         <v>215</v>
@@ -5526,7 +5538,7 @@
         <v>10</v>
       </c>
       <c r="F102">
-        <v>263</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -5534,19 +5546,19 @@
         <v>216</v>
       </c>
       <c r="B103" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C103" t="s">
         <v>217</v>
       </c>
       <c r="D103" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E103" t="s">
         <v>10</v>
       </c>
       <c r="F103">
-        <v>181</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -5554,19 +5566,19 @@
         <v>218</v>
       </c>
       <c r="B104" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C104" t="s">
         <v>219</v>
       </c>
       <c r="D104" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E104" t="s">
         <v>10</v>
       </c>
       <c r="F104">
-        <v>209</v>
+        <v>163</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -5574,19 +5586,19 @@
         <v>220</v>
       </c>
       <c r="B105" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C105" t="s">
         <v>221</v>
       </c>
       <c r="D105" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E105" t="s">
         <v>10</v>
       </c>
       <c r="F105">
-        <v>281</v>
+        <v>158</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -5594,19 +5606,19 @@
         <v>222</v>
       </c>
       <c r="B106" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C106" t="s">
         <v>223</v>
       </c>
       <c r="D106" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E106" t="s">
         <v>10</v>
       </c>
       <c r="F106">
-        <v>198</v>
+        <v>163</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -5614,19 +5626,19 @@
         <v>224</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C107" t="s">
         <v>225</v>
       </c>
       <c r="D107" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E107" t="s">
         <v>10</v>
       </c>
       <c r="F107">
-        <v>257</v>
+        <v>168</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -5634,99 +5646,99 @@
         <v>226</v>
       </c>
       <c r="B108" t="s">
+        <v>194</v>
+      </c>
+      <c r="C108" t="s">
         <v>227</v>
       </c>
-      <c r="C108" t="s">
-        <v>228</v>
-      </c>
       <c r="D108" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E108" t="s">
         <v>10</v>
       </c>
       <c r="F108">
-        <v>260</v>
+        <v>240</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>228</v>
+      </c>
+      <c r="B109" t="s">
+        <v>194</v>
+      </c>
+      <c r="C109" t="s">
         <v>229</v>
       </c>
-      <c r="B109" t="s">
-        <v>227</v>
-      </c>
-      <c r="C109" t="s">
-        <v>230</v>
-      </c>
       <c r="D109" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E109" t="s">
         <v>10</v>
       </c>
       <c r="F109">
-        <v>133</v>
+        <v>113</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>230</v>
+      </c>
+      <c r="B110" t="s">
+        <v>194</v>
+      </c>
+      <c r="C110" t="s">
         <v>231</v>
       </c>
-      <c r="B110" t="s">
-        <v>227</v>
-      </c>
-      <c r="C110" t="s">
-        <v>232</v>
-      </c>
       <c r="D110" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E110" t="s">
         <v>10</v>
       </c>
       <c r="F110">
-        <v>180</v>
+        <v>131</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>232</v>
+      </c>
+      <c r="B111" t="s">
+        <v>194</v>
+      </c>
+      <c r="C111" t="s">
         <v>233</v>
       </c>
-      <c r="B111" t="s">
-        <v>227</v>
-      </c>
-      <c r="C111" t="s">
-        <v>234</v>
-      </c>
       <c r="D111" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E111" t="s">
         <v>10</v>
       </c>
       <c r="F111">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>234</v>
+      </c>
+      <c r="B112" t="s">
         <v>235</v>
-      </c>
-      <c r="B112" t="s">
-        <v>227</v>
       </c>
       <c r="C112" t="s">
         <v>236</v>
       </c>
       <c r="D112" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E112" t="s">
         <v>10</v>
       </c>
       <c r="F112">
-        <v>194</v>
+        <v>261</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -5734,19 +5746,19 @@
         <v>237</v>
       </c>
       <c r="B113" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C113" t="s">
         <v>238</v>
       </c>
       <c r="D113" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E113" t="s">
         <v>10</v>
       </c>
       <c r="F113">
-        <v>287</v>
+        <v>239</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -5754,19 +5766,19 @@
         <v>239</v>
       </c>
       <c r="B114" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C114" t="s">
         <v>240</v>
       </c>
       <c r="D114" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E114" t="s">
         <v>10</v>
       </c>
       <c r="F114">
-        <v>271</v>
+        <v>233</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -5774,19 +5786,19 @@
         <v>241</v>
       </c>
       <c r="B115" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C115" t="s">
         <v>242</v>
       </c>
       <c r="D115" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E115" t="s">
         <v>10</v>
       </c>
       <c r="F115">
-        <v>149</v>
+        <v>117</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -5794,19 +5806,19 @@
         <v>243</v>
       </c>
       <c r="B116" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C116" t="s">
         <v>244</v>
       </c>
       <c r="D116" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E116" t="s">
         <v>10</v>
       </c>
       <c r="F116">
-        <v>295</v>
+        <v>228</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -5814,19 +5826,19 @@
         <v>245</v>
       </c>
       <c r="B117" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C117" t="s">
         <v>246</v>
       </c>
       <c r="D117" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E117" t="s">
         <v>10</v>
       </c>
       <c r="F117">
-        <v>145</v>
+        <v>118</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -5834,19 +5846,19 @@
         <v>247</v>
       </c>
       <c r="B118" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C118" t="s">
         <v>248</v>
       </c>
       <c r="D118" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E118" t="s">
         <v>10</v>
       </c>
       <c r="F118">
-        <v>253</v>
+        <v>115</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -5854,19 +5866,19 @@
         <v>249</v>
       </c>
       <c r="B119" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C119" t="s">
         <v>250</v>
       </c>
       <c r="D119" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E119" t="s">
         <v>10</v>
       </c>
       <c r="F119">
-        <v>194</v>
+        <v>138</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -5874,19 +5886,19 @@
         <v>251</v>
       </c>
       <c r="B120" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C120" t="s">
         <v>252</v>
       </c>
       <c r="D120" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E120" t="s">
         <v>10</v>
       </c>
       <c r="F120">
-        <v>175</v>
+        <v>288</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -5894,19 +5906,19 @@
         <v>253</v>
       </c>
       <c r="B121" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C121" t="s">
         <v>254</v>
       </c>
       <c r="D121" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E121" t="s">
         <v>10</v>
       </c>
       <c r="F121">
-        <v>164</v>
+        <v>100</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -5914,19 +5926,19 @@
         <v>255</v>
       </c>
       <c r="B122" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C122" t="s">
         <v>256</v>
       </c>
       <c r="D122" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E122" t="s">
         <v>10</v>
       </c>
       <c r="F122">
-        <v>292</v>
+        <v>150</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -5934,19 +5946,19 @@
         <v>257</v>
       </c>
       <c r="B123" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C123" t="s">
         <v>258</v>
       </c>
       <c r="D123" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E123" t="s">
         <v>10</v>
       </c>
       <c r="F123">
-        <v>119</v>
+        <v>239</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -5954,19 +5966,19 @@
         <v>259</v>
       </c>
       <c r="B124" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C124" t="s">
         <v>260</v>
       </c>
       <c r="D124" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E124" t="s">
         <v>10</v>
       </c>
       <c r="F124">
-        <v>261</v>
+        <v>246</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -5974,19 +5986,19 @@
         <v>261</v>
       </c>
       <c r="B125" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C125" t="s">
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E125" t="s">
         <v>10</v>
       </c>
       <c r="F125">
-        <v>198</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -5994,19 +6006,19 @@
         <v>263</v>
       </c>
       <c r="B126" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C126" t="s">
         <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E126" t="s">
         <v>10</v>
       </c>
       <c r="F126">
-        <v>222</v>
+        <v>157</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -6014,19 +6026,19 @@
         <v>265</v>
       </c>
       <c r="B127" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C127" t="s">
         <v>266</v>
       </c>
       <c r="D127" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E127" t="s">
         <v>10</v>
       </c>
       <c r="F127">
-        <v>220</v>
+        <v>248</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -6034,19 +6046,19 @@
         <v>267</v>
       </c>
       <c r="B128" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C128" t="s">
         <v>268</v>
       </c>
       <c r="D128" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E128" t="s">
         <v>10</v>
       </c>
       <c r="F128">
-        <v>230</v>
+        <v>276</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -6054,19 +6066,19 @@
         <v>269</v>
       </c>
       <c r="B129" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C129" t="s">
         <v>270</v>
       </c>
       <c r="D129" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E129" t="s">
         <v>10</v>
       </c>
       <c r="F129">
-        <v>245</v>
+        <v>230</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -6074,19 +6086,19 @@
         <v>271</v>
       </c>
       <c r="B130" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C130" t="s">
         <v>272</v>
       </c>
       <c r="D130" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E130" t="s">
         <v>10</v>
       </c>
       <c r="F130">
-        <v>290</v>
+        <v>214</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -6094,19 +6106,19 @@
         <v>273</v>
       </c>
       <c r="B131" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C131" t="s">
         <v>274</v>
       </c>
       <c r="D131" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E131" t="s">
         <v>10</v>
       </c>
       <c r="F131">
-        <v>118</v>
+        <v>203</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -6114,19 +6126,19 @@
         <v>275</v>
       </c>
       <c r="B132" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C132" t="s">
         <v>276</v>
       </c>
       <c r="D132" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E132" t="s">
         <v>10</v>
       </c>
       <c r="F132">
-        <v>221</v>
+        <v>167</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -6134,19 +6146,19 @@
         <v>277</v>
       </c>
       <c r="B133" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C133" t="s">
         <v>278</v>
       </c>
       <c r="D133" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E133" t="s">
         <v>10</v>
       </c>
       <c r="F133">
-        <v>136</v>
+        <v>183</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -6154,19 +6166,19 @@
         <v>279</v>
       </c>
       <c r="B134" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C134" t="s">
         <v>280</v>
       </c>
       <c r="D134" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
       </c>
       <c r="F134">
-        <v>126</v>
+        <v>194</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -6174,19 +6186,19 @@
         <v>281</v>
       </c>
       <c r="B135" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C135" t="s">
         <v>282</v>
       </c>
       <c r="D135" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E135" t="s">
         <v>10</v>
       </c>
       <c r="F135">
-        <v>199</v>
+        <v>161</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -6194,19 +6206,19 @@
         <v>283</v>
       </c>
       <c r="B136" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C136" t="s">
         <v>284</v>
       </c>
       <c r="D136" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E136" t="s">
         <v>10</v>
       </c>
       <c r="F136">
-        <v>199</v>
+        <v>245</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -6214,19 +6226,19 @@
         <v>285</v>
       </c>
       <c r="B137" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C137" t="s">
         <v>286</v>
       </c>
       <c r="D137" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E137" t="s">
         <v>10</v>
       </c>
       <c r="F137">
-        <v>146</v>
+        <v>190</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -6234,59 +6246,59 @@
         <v>287</v>
       </c>
       <c r="B138" t="s">
+        <v>235</v>
+      </c>
+      <c r="C138" t="s">
         <v>288</v>
       </c>
-      <c r="C138" t="s">
-        <v>289</v>
-      </c>
       <c r="D138" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E138" t="s">
         <v>10</v>
       </c>
       <c r="F138">
-        <v>287</v>
+        <v>125</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>289</v>
+      </c>
+      <c r="B139" t="s">
+        <v>235</v>
+      </c>
+      <c r="C139" t="s">
         <v>290</v>
       </c>
-      <c r="B139" t="s">
-        <v>288</v>
-      </c>
-      <c r="C139" t="s">
-        <v>291</v>
-      </c>
       <c r="D139" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E139" t="s">
         <v>10</v>
       </c>
       <c r="F139">
-        <v>185</v>
+        <v>209</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>291</v>
+      </c>
+      <c r="B140" t="s">
         <v>292</v>
-      </c>
-      <c r="B140" t="s">
-        <v>288</v>
       </c>
       <c r="C140" t="s">
         <v>293</v>
       </c>
       <c r="D140" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
       </c>
       <c r="F140">
-        <v>283</v>
+        <v>131</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -6294,19 +6306,19 @@
         <v>294</v>
       </c>
       <c r="B141" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C141" t="s">
         <v>295</v>
       </c>
       <c r="D141" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
       </c>
       <c r="F141">
-        <v>129</v>
+        <v>270</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -6314,19 +6326,19 @@
         <v>296</v>
       </c>
       <c r="B142" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C142" t="s">
         <v>297</v>
       </c>
       <c r="D142" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
       </c>
       <c r="F142">
-        <v>290</v>
+        <v>281</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -6334,19 +6346,19 @@
         <v>298</v>
       </c>
       <c r="B143" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C143" t="s">
         <v>299</v>
       </c>
       <c r="D143" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
       </c>
       <c r="F143">
-        <v>283</v>
+        <v>263</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -6354,19 +6366,19 @@
         <v>300</v>
       </c>
       <c r="B144" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C144" t="s">
         <v>301</v>
       </c>
       <c r="D144" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E144" t="s">
         <v>10</v>
       </c>
       <c r="F144">
-        <v>292</v>
+        <v>190</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -6374,19 +6386,19 @@
         <v>302</v>
       </c>
       <c r="B145" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C145" t="s">
         <v>303</v>
       </c>
       <c r="D145" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E145" t="s">
         <v>10</v>
       </c>
       <c r="F145">
-        <v>207</v>
+        <v>250</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -6394,19 +6406,19 @@
         <v>304</v>
       </c>
       <c r="B146" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C146" t="s">
         <v>305</v>
       </c>
       <c r="D146" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
       </c>
       <c r="F146">
-        <v>195</v>
+        <v>101</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -6414,19 +6426,19 @@
         <v>306</v>
       </c>
       <c r="B147" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C147" t="s">
         <v>307</v>
       </c>
       <c r="D147" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E147" t="s">
         <v>10</v>
       </c>
       <c r="F147">
-        <v>242</v>
+        <v>217</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -6434,19 +6446,19 @@
         <v>308</v>
       </c>
       <c r="B148" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C148" t="s">
         <v>309</v>
       </c>
       <c r="D148" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E148" t="s">
         <v>10</v>
       </c>
       <c r="F148">
-        <v>223</v>
+        <v>281</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -6454,19 +6466,19 @@
         <v>310</v>
       </c>
       <c r="B149" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C149" t="s">
         <v>311</v>
       </c>
       <c r="D149" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E149" t="s">
         <v>10</v>
       </c>
       <c r="F149">
-        <v>214</v>
+        <v>287</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -6474,19 +6486,19 @@
         <v>312</v>
       </c>
       <c r="B150" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C150" t="s">
         <v>313</v>
       </c>
       <c r="D150" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E150" t="s">
         <v>10</v>
       </c>
       <c r="F150">
-        <v>241</v>
+        <v>231</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -6494,19 +6506,19 @@
         <v>314</v>
       </c>
       <c r="B151" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C151" t="s">
         <v>315</v>
       </c>
       <c r="D151" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E151" t="s">
         <v>10</v>
       </c>
       <c r="F151">
-        <v>203</v>
+        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -6514,19 +6526,19 @@
         <v>316</v>
       </c>
       <c r="B152" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C152" t="s">
         <v>317</v>
       </c>
       <c r="D152" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E152" t="s">
         <v>10</v>
       </c>
       <c r="F152">
-        <v>210</v>
+        <v>283</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -6534,19 +6546,19 @@
         <v>318</v>
       </c>
       <c r="B153" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C153" t="s">
         <v>319</v>
       </c>
       <c r="D153" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E153" t="s">
         <v>10</v>
       </c>
       <c r="F153">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -6554,19 +6566,19 @@
         <v>320</v>
       </c>
       <c r="B154" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C154" t="s">
         <v>321</v>
       </c>
       <c r="D154" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E154" t="s">
         <v>10</v>
       </c>
       <c r="F154">
-        <v>216</v>
+        <v>115</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -6574,19 +6586,19 @@
         <v>322</v>
       </c>
       <c r="B155" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C155" t="s">
         <v>323</v>
       </c>
       <c r="D155" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E155" t="s">
         <v>10</v>
       </c>
       <c r="F155">
-        <v>294</v>
+        <v>248</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -6594,19 +6606,19 @@
         <v>324</v>
       </c>
       <c r="B156" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C156" t="s">
         <v>325</v>
       </c>
       <c r="D156" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E156" t="s">
         <v>10</v>
       </c>
       <c r="F156">
-        <v>193</v>
+        <v>246</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -6614,19 +6626,19 @@
         <v>326</v>
       </c>
       <c r="B157" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C157" t="s">
         <v>327</v>
       </c>
       <c r="D157" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E157" t="s">
         <v>10</v>
       </c>
       <c r="F157">
-        <v>228</v>
+        <v>160</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -6634,39 +6646,39 @@
         <v>328</v>
       </c>
       <c r="B158" t="s">
+        <v>292</v>
+      </c>
+      <c r="C158" t="s">
         <v>329</v>
       </c>
-      <c r="C158" t="s">
-        <v>330</v>
-      </c>
       <c r="D158" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E158" t="s">
         <v>10</v>
       </c>
       <c r="F158">
-        <v>265</v>
+        <v>237</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>330</v>
+      </c>
+      <c r="B159" t="s">
         <v>331</v>
-      </c>
-      <c r="B159" t="s">
-        <v>329</v>
       </c>
       <c r="C159" t="s">
         <v>332</v>
       </c>
       <c r="D159" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E159" t="s">
         <v>10</v>
       </c>
       <c r="F159">
-        <v>218</v>
+        <v>292</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -6674,19 +6686,19 @@
         <v>333</v>
       </c>
       <c r="B160" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C160" t="s">
         <v>334</v>
       </c>
       <c r="D160" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E160" t="s">
         <v>10</v>
       </c>
       <c r="F160">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -6694,19 +6706,19 @@
         <v>335</v>
       </c>
       <c r="B161" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C161" t="s">
         <v>336</v>
       </c>
       <c r="D161" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
       </c>
       <c r="F161">
-        <v>201</v>
+        <v>285</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -6714,19 +6726,19 @@
         <v>337</v>
       </c>
       <c r="B162" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C162" t="s">
         <v>338</v>
       </c>
       <c r="D162" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E162" t="s">
         <v>10</v>
       </c>
       <c r="F162">
-        <v>155</v>
+        <v>176</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -6734,19 +6746,19 @@
         <v>339</v>
       </c>
       <c r="B163" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C163" t="s">
         <v>340</v>
       </c>
       <c r="D163" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E163" t="s">
         <v>10</v>
       </c>
       <c r="F163">
-        <v>112</v>
+        <v>202</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -6754,19 +6766,19 @@
         <v>341</v>
       </c>
       <c r="B164" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C164" t="s">
         <v>342</v>
       </c>
       <c r="D164" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E164" t="s">
         <v>10</v>
       </c>
       <c r="F164">
-        <v>219</v>
+        <v>100</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -6774,19 +6786,19 @@
         <v>343</v>
       </c>
       <c r="B165" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C165" t="s">
         <v>344</v>
       </c>
       <c r="D165" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E165" t="s">
         <v>10</v>
       </c>
       <c r="F165">
-        <v>219</v>
+        <v>271</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -6794,7 +6806,7 @@
         <v>345</v>
       </c>
       <c r="B166" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C166" t="s">
         <v>346</v>
@@ -6806,7 +6818,7 @@
         <v>10</v>
       </c>
       <c r="F166">
-        <v>162</v>
+        <v>292</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -6814,7 +6826,7 @@
         <v>347</v>
       </c>
       <c r="B167" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C167" t="s">
         <v>348</v>
@@ -6826,7 +6838,7 @@
         <v>10</v>
       </c>
       <c r="F167">
-        <v>202</v>
+        <v>128</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -6834,7 +6846,7 @@
         <v>349</v>
       </c>
       <c r="B168" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C168" t="s">
         <v>350</v>
@@ -6846,7 +6858,7 @@
         <v>10</v>
       </c>
       <c r="F168">
-        <v>200</v>
+        <v>129</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -6854,7 +6866,7 @@
         <v>351</v>
       </c>
       <c r="B169" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C169" t="s">
         <v>352</v>
@@ -6866,7 +6878,7 @@
         <v>10</v>
       </c>
       <c r="F169">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -6874,7 +6886,7 @@
         <v>353</v>
       </c>
       <c r="B170" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C170" t="s">
         <v>354</v>
@@ -6886,7 +6898,7 @@
         <v>10</v>
       </c>
       <c r="F170">
-        <v>148</v>
+        <v>108</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -6894,7 +6906,7 @@
         <v>355</v>
       </c>
       <c r="B171" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C171" t="s">
         <v>356</v>
@@ -6906,7 +6918,7 @@
         <v>10</v>
       </c>
       <c r="F171">
-        <v>200</v>
+        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -6914,7 +6926,7 @@
         <v>357</v>
       </c>
       <c r="B172" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C172" t="s">
         <v>358</v>
@@ -6926,7 +6938,7 @@
         <v>10</v>
       </c>
       <c r="F172">
-        <v>298</v>
+        <v>167</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -6934,7 +6946,7 @@
         <v>359</v>
       </c>
       <c r="B173" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C173" t="s">
         <v>360</v>
@@ -6946,7 +6958,7 @@
         <v>10</v>
       </c>
       <c r="F173">
-        <v>202</v>
+        <v>177</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -6954,7 +6966,7 @@
         <v>361</v>
       </c>
       <c r="B174" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C174" t="s">
         <v>362</v>
@@ -6966,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="F174">
-        <v>229</v>
+        <v>209</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6974,7 +6986,7 @@
         <v>363</v>
       </c>
       <c r="B175" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C175" t="s">
         <v>364</v>
@@ -6986,7 +6998,7 @@
         <v>10</v>
       </c>
       <c r="F175">
-        <v>141</v>
+        <v>284</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -6994,7 +7006,7 @@
         <v>365</v>
       </c>
       <c r="B176" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C176" t="s">
         <v>366</v>
@@ -7006,7 +7018,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>264</v>
+        <v>148</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -7014,7 +7026,7 @@
         <v>367</v>
       </c>
       <c r="B177" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C177" t="s">
         <v>368</v>
@@ -7026,7 +7038,7 @@
         <v>10</v>
       </c>
       <c r="F177">
-        <v>267</v>
+        <v>209</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -7034,7 +7046,7 @@
         <v>369</v>
       </c>
       <c r="B178" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C178" t="s">
         <v>370</v>
@@ -7046,7 +7058,7 @@
         <v>10</v>
       </c>
       <c r="F178">
-        <v>183</v>
+        <v>256</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -7054,7 +7066,7 @@
         <v>371</v>
       </c>
       <c r="B179" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C179" t="s">
         <v>372</v>
@@ -7066,7 +7078,7 @@
         <v>10</v>
       </c>
       <c r="F179">
-        <v>182</v>
+        <v>206</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -7074,7 +7086,7 @@
         <v>373</v>
       </c>
       <c r="B180" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C180" t="s">
         <v>374</v>
@@ -7086,7 +7098,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>133</v>
+        <v>267</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -7094,7 +7106,7 @@
         <v>375</v>
       </c>
       <c r="B181" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C181" t="s">
         <v>376</v>
@@ -7106,7 +7118,7 @@
         <v>10</v>
       </c>
       <c r="F181">
-        <v>216</v>
+        <v>235</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -7114,7 +7126,7 @@
         <v>377</v>
       </c>
       <c r="B182" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C182" t="s">
         <v>378</v>
@@ -7126,7 +7138,7 @@
         <v>10</v>
       </c>
       <c r="F182">
-        <v>226</v>
+        <v>253</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -7134,7 +7146,7 @@
         <v>379</v>
       </c>
       <c r="B183" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C183" t="s">
         <v>380</v>
@@ -7146,7 +7158,7 @@
         <v>10</v>
       </c>
       <c r="F183">
-        <v>221</v>
+        <v>114</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -7154,7 +7166,7 @@
         <v>381</v>
       </c>
       <c r="B184" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C184" t="s">
         <v>382</v>
@@ -7166,7 +7178,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>191</v>
+        <v>268</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -7174,7 +7186,7 @@
         <v>383</v>
       </c>
       <c r="B185" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C185" t="s">
         <v>384</v>
@@ -7194,7 +7206,7 @@
         <v>385</v>
       </c>
       <c r="B186" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C186" t="s">
         <v>386</v>
@@ -7206,7 +7218,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>141</v>
+        <v>252</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -7214,7 +7226,7 @@
         <v>387</v>
       </c>
       <c r="B187" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C187" t="s">
         <v>388</v>
@@ -7226,7 +7238,7 @@
         <v>10</v>
       </c>
       <c r="F187">
-        <v>261</v>
+        <v>249</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -7234,7 +7246,7 @@
         <v>389</v>
       </c>
       <c r="B188" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C188" t="s">
         <v>390</v>
@@ -7246,7 +7258,7 @@
         <v>10</v>
       </c>
       <c r="F188">
-        <v>273</v>
+        <v>247</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -7254,7 +7266,7 @@
         <v>391</v>
       </c>
       <c r="B189" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C189" t="s">
         <v>392</v>
@@ -7266,7 +7278,7 @@
         <v>10</v>
       </c>
       <c r="F189">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -7274,7 +7286,7 @@
         <v>393</v>
       </c>
       <c r="B190" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C190" t="s">
         <v>394</v>
@@ -7286,7 +7298,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>176</v>
+        <v>275</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -7294,7 +7306,7 @@
         <v>395</v>
       </c>
       <c r="B191" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C191" t="s">
         <v>396</v>
@@ -7306,7 +7318,7 @@
         <v>10</v>
       </c>
       <c r="F191">
-        <v>165</v>
+        <v>196</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -7314,7 +7326,7 @@
         <v>397</v>
       </c>
       <c r="B192" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C192" t="s">
         <v>398</v>
@@ -7326,7 +7338,7 @@
         <v>10</v>
       </c>
       <c r="F192">
-        <v>172</v>
+        <v>104</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -7334,7 +7346,7 @@
         <v>399</v>
       </c>
       <c r="B193" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C193" t="s">
         <v>400</v>
@@ -7346,7 +7358,7 @@
         <v>10</v>
       </c>
       <c r="F193">
-        <v>202</v>
+        <v>288</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -7354,7 +7366,7 @@
         <v>401</v>
       </c>
       <c r="B194" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C194" t="s">
         <v>402</v>
@@ -7366,7 +7378,7 @@
         <v>10</v>
       </c>
       <c r="F194">
-        <v>195</v>
+        <v>127</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -7374,7 +7386,7 @@
         <v>403</v>
       </c>
       <c r="B195" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C195" t="s">
         <v>404</v>
@@ -7386,7 +7398,7 @@
         <v>10</v>
       </c>
       <c r="F195">
-        <v>281</v>
+        <v>100</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -7394,7 +7406,7 @@
         <v>405</v>
       </c>
       <c r="B196" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C196" t="s">
         <v>406</v>
@@ -7406,7 +7418,7 @@
         <v>10</v>
       </c>
       <c r="F196">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -7414,7 +7426,7 @@
         <v>407</v>
       </c>
       <c r="B197" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C197" t="s">
         <v>408</v>
@@ -7426,7 +7438,7 @@
         <v>10</v>
       </c>
       <c r="F197">
-        <v>238</v>
+        <v>136</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -7446,7 +7458,7 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>270</v>
+        <v>138</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -7466,7 +7478,7 @@
         <v>10</v>
       </c>
       <c r="F199">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -7486,7 +7498,7 @@
         <v>10</v>
       </c>
       <c r="F200">
-        <v>286</v>
+        <v>190</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -7506,7 +7518,7 @@
         <v>10</v>
       </c>
       <c r="F201">
-        <v>247</v>
+        <v>193</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -7526,7 +7538,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>206</v>
+        <v>289</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -7546,7 +7558,7 @@
         <v>10</v>
       </c>
       <c r="F203">
-        <v>129</v>
+        <v>273</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -7566,7 +7578,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>228</v>
+        <v>128</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -7586,7 +7598,7 @@
         <v>10</v>
       </c>
       <c r="F205">
-        <v>133</v>
+        <v>263</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -7606,7 +7618,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>144</v>
+        <v>285</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -7626,7 +7638,7 @@
         <v>10</v>
       </c>
       <c r="F207">
-        <v>292</v>
+        <v>180</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -7646,7 +7658,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>141</v>
+        <v>235</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -7666,7 +7678,7 @@
         <v>10</v>
       </c>
       <c r="F209">
-        <v>254</v>
+        <v>188</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -7686,7 +7698,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>283</v>
+        <v>250</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -7706,7 +7718,7 @@
         <v>10</v>
       </c>
       <c r="F211">
-        <v>169</v>
+        <v>132</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -7726,7 +7738,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>170</v>
+        <v>241</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -7746,7 +7758,7 @@
         <v>10</v>
       </c>
       <c r="F213">
-        <v>297</v>
+        <v>236</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -7766,7 +7778,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -7786,7 +7798,7 @@
         <v>10</v>
       </c>
       <c r="F215">
-        <v>157</v>
+        <v>129</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -7800,13 +7812,13 @@
         <v>447</v>
       </c>
       <c r="D216" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E216" t="s">
         <v>10</v>
       </c>
       <c r="F216">
-        <v>278</v>
+        <v>214</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -7820,13 +7832,13 @@
         <v>449</v>
       </c>
       <c r="D217" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E217" t="s">
         <v>10</v>
       </c>
       <c r="F217">
-        <v>296</v>
+        <v>214</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -7840,13 +7852,13 @@
         <v>451</v>
       </c>
       <c r="D218" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E218" t="s">
         <v>10</v>
       </c>
       <c r="F218">
-        <v>206</v>
+        <v>262</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -7860,13 +7872,13 @@
         <v>453</v>
       </c>
       <c r="D219" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E219" t="s">
         <v>10</v>
       </c>
       <c r="F219">
-        <v>263</v>
+        <v>103</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -7880,13 +7892,13 @@
         <v>455</v>
       </c>
       <c r="D220" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E220" t="s">
         <v>10</v>
       </c>
       <c r="F220">
-        <v>196</v>
+        <v>260</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -7900,13 +7912,13 @@
         <v>457</v>
       </c>
       <c r="D221" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E221" t="s">
         <v>10</v>
       </c>
       <c r="F221">
-        <v>122</v>
+        <v>150</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -7920,13 +7932,13 @@
         <v>459</v>
       </c>
       <c r="D222" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E222" t="s">
         <v>10</v>
       </c>
       <c r="F222">
-        <v>268</v>
+        <v>149</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7940,13 +7952,13 @@
         <v>461</v>
       </c>
       <c r="D223" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E223" t="s">
         <v>10</v>
       </c>
       <c r="F223">
-        <v>222</v>
+        <v>177</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7960,13 +7972,13 @@
         <v>463</v>
       </c>
       <c r="D224" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E224" t="s">
         <v>10</v>
       </c>
       <c r="F224">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7986,7 +7998,7 @@
         <v>10</v>
       </c>
       <c r="F225">
-        <v>294</v>
+        <v>248</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -8006,7 +8018,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>192</v>
+        <v>159</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -8026,7 +8038,7 @@
         <v>10</v>
       </c>
       <c r="F227">
-        <v>156</v>
+        <v>128</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -8046,7 +8058,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>151</v>
+        <v>266</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -8086,7 +8098,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>132</v>
+        <v>217</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -8106,7 +8118,7 @@
         <v>10</v>
       </c>
       <c r="F231">
-        <v>169</v>
+        <v>112</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -8126,7 +8138,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>100</v>
+        <v>154</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -8146,7 +8158,7 @@
         <v>10</v>
       </c>
       <c r="F233">
-        <v>287</v>
+        <v>150</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -8166,7 +8178,7 @@
         <v>10</v>
       </c>
       <c r="F234">
-        <v>245</v>
+        <v>108</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -8186,7 +8198,7 @@
         <v>10</v>
       </c>
       <c r="F235">
-        <v>191</v>
+        <v>116</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -8206,7 +8218,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -8226,7 +8238,7 @@
         <v>10</v>
       </c>
       <c r="F237">
-        <v>190</v>
+        <v>105</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -8246,7 +8258,7 @@
         <v>10</v>
       </c>
       <c r="F238">
-        <v>237</v>
+        <v>152</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -8266,7 +8278,7 @@
         <v>10</v>
       </c>
       <c r="F239">
-        <v>231</v>
+        <v>109</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -8286,7 +8298,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>272</v>
+        <v>219</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -8300,13 +8312,13 @@
         <v>498</v>
       </c>
       <c r="D241" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E241" t="s">
         <v>10</v>
       </c>
       <c r="F241">
-        <v>216</v>
+        <v>179</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -8320,13 +8332,13 @@
         <v>500</v>
       </c>
       <c r="D242" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E242" t="s">
         <v>10</v>
       </c>
       <c r="F242">
-        <v>165</v>
+        <v>179</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -8340,13 +8352,13 @@
         <v>502</v>
       </c>
       <c r="D243" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E243" t="s">
         <v>10</v>
       </c>
       <c r="F243">
-        <v>169</v>
+        <v>133</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -8360,13 +8372,13 @@
         <v>504</v>
       </c>
       <c r="D244" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E244" t="s">
         <v>10</v>
       </c>
       <c r="F244">
-        <v>212</v>
+        <v>276</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -8380,13 +8392,13 @@
         <v>506</v>
       </c>
       <c r="D245" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E245" t="s">
         <v>10</v>
       </c>
       <c r="F245">
-        <v>116</v>
+        <v>192</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -8400,13 +8412,13 @@
         <v>508</v>
       </c>
       <c r="D246" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E246" t="s">
         <v>10</v>
       </c>
       <c r="F246">
-        <v>231</v>
+        <v>143</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -8420,13 +8432,13 @@
         <v>510</v>
       </c>
       <c r="D247" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E247" t="s">
         <v>10</v>
       </c>
       <c r="F247">
-        <v>148</v>
+        <v>275</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -8440,13 +8452,13 @@
         <v>512</v>
       </c>
       <c r="D248" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E248" t="s">
         <v>10</v>
       </c>
       <c r="F248">
-        <v>143</v>
+        <v>160</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -8460,13 +8472,13 @@
         <v>514</v>
       </c>
       <c r="D249" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E249" t="s">
         <v>10</v>
       </c>
       <c r="F249">
-        <v>292</v>
+        <v>201</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -8480,13 +8492,13 @@
         <v>516</v>
       </c>
       <c r="D250" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E250" t="s">
         <v>10</v>
       </c>
       <c r="F250">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -8500,13 +8512,13 @@
         <v>518</v>
       </c>
       <c r="D251" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E251" t="s">
         <v>10</v>
       </c>
       <c r="F251">
-        <v>185</v>
+        <v>114</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -8520,13 +8532,13 @@
         <v>520</v>
       </c>
       <c r="D252" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E252" t="s">
         <v>10</v>
       </c>
       <c r="F252">
-        <v>221</v>
+        <v>200</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -8540,13 +8552,13 @@
         <v>522</v>
       </c>
       <c r="D253" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E253" t="s">
         <v>10</v>
       </c>
       <c r="F253">
-        <v>224</v>
+        <v>287</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -8560,13 +8572,13 @@
         <v>524</v>
       </c>
       <c r="D254" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E254" t="s">
         <v>10</v>
       </c>
       <c r="F254">
-        <v>140</v>
+        <v>106</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -8580,13 +8592,13 @@
         <v>526</v>
       </c>
       <c r="D255" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E255" t="s">
         <v>10</v>
       </c>
       <c r="F255">
-        <v>124</v>
+        <v>259</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -8594,39 +8606,39 @@
         <v>527</v>
       </c>
       <c r="B256" t="s">
-        <v>489</v>
+        <v>528</v>
       </c>
       <c r="C256" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D256" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E256" t="s">
         <v>10</v>
       </c>
       <c r="F256">
-        <v>111</v>
+        <v>191</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B257" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C257" t="s">
         <v>531</v>
       </c>
       <c r="D257" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E257" t="s">
         <v>10</v>
       </c>
       <c r="F257">
-        <v>176</v>
+        <v>103</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -8634,19 +8646,19 @@
         <v>532</v>
       </c>
       <c r="B258" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C258" t="s">
         <v>533</v>
       </c>
       <c r="D258" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E258" t="s">
         <v>10</v>
       </c>
       <c r="F258">
-        <v>110</v>
+        <v>142</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -8654,19 +8666,19 @@
         <v>534</v>
       </c>
       <c r="B259" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C259" t="s">
         <v>535</v>
       </c>
       <c r="D259" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E259" t="s">
         <v>10</v>
       </c>
       <c r="F259">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -8674,19 +8686,19 @@
         <v>536</v>
       </c>
       <c r="B260" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C260" t="s">
         <v>537</v>
       </c>
       <c r="D260" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E260" t="s">
         <v>10</v>
       </c>
       <c r="F260">
-        <v>221</v>
+        <v>157</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -8694,19 +8706,19 @@
         <v>538</v>
       </c>
       <c r="B261" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C261" t="s">
         <v>539</v>
       </c>
       <c r="D261" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E261" t="s">
         <v>10</v>
       </c>
       <c r="F261">
-        <v>260</v>
+        <v>165</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -8714,19 +8726,19 @@
         <v>540</v>
       </c>
       <c r="B262" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C262" t="s">
         <v>541</v>
       </c>
       <c r="D262" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E262" t="s">
         <v>10</v>
       </c>
       <c r="F262">
-        <v>147</v>
+        <v>290</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -8734,19 +8746,19 @@
         <v>542</v>
       </c>
       <c r="B263" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C263" t="s">
         <v>543</v>
       </c>
       <c r="D263" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E263" t="s">
         <v>10</v>
       </c>
       <c r="F263">
-        <v>132</v>
+        <v>252</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -8754,19 +8766,19 @@
         <v>544</v>
       </c>
       <c r="B264" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C264" t="s">
         <v>545</v>
       </c>
       <c r="D264" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E264" t="s">
         <v>10</v>
       </c>
       <c r="F264">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -8774,19 +8786,19 @@
         <v>546</v>
       </c>
       <c r="B265" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C265" t="s">
         <v>547</v>
       </c>
       <c r="D265" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E265" t="s">
         <v>10</v>
       </c>
       <c r="F265">
-        <v>124</v>
+        <v>150</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -8794,19 +8806,19 @@
         <v>548</v>
       </c>
       <c r="B266" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C266" t="s">
         <v>549</v>
       </c>
       <c r="D266" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E266" t="s">
         <v>10</v>
       </c>
       <c r="F266">
-        <v>133</v>
+        <v>106</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -8814,19 +8826,19 @@
         <v>550</v>
       </c>
       <c r="B267" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C267" t="s">
         <v>551</v>
       </c>
       <c r="D267" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E267" t="s">
         <v>10</v>
       </c>
       <c r="F267">
-        <v>246</v>
+        <v>172</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -8834,19 +8846,19 @@
         <v>552</v>
       </c>
       <c r="B268" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C268" t="s">
         <v>553</v>
       </c>
       <c r="D268" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E268" t="s">
         <v>10</v>
       </c>
       <c r="F268">
-        <v>204</v>
+        <v>222</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -8854,19 +8866,19 @@
         <v>554</v>
       </c>
       <c r="B269" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C269" t="s">
         <v>555</v>
       </c>
       <c r="D269" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E269" t="s">
         <v>10</v>
       </c>
       <c r="F269">
-        <v>170</v>
+        <v>142</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -8874,19 +8886,19 @@
         <v>556</v>
       </c>
       <c r="B270" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C270" t="s">
         <v>557</v>
       </c>
       <c r="D270" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E270" t="s">
         <v>10</v>
       </c>
       <c r="F270">
-        <v>291</v>
+        <v>227</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -8894,19 +8906,19 @@
         <v>558</v>
       </c>
       <c r="B271" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C271" t="s">
         <v>559</v>
       </c>
       <c r="D271" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E271" t="s">
         <v>10</v>
       </c>
       <c r="F271">
-        <v>127</v>
+        <v>173</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -8914,19 +8926,19 @@
         <v>560</v>
       </c>
       <c r="B272" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C272" t="s">
         <v>561</v>
       </c>
       <c r="D272" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E272" t="s">
         <v>10</v>
       </c>
       <c r="F272">
-        <v>192</v>
+        <v>126</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -8934,19 +8946,19 @@
         <v>562</v>
       </c>
       <c r="B273" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C273" t="s">
         <v>563</v>
       </c>
       <c r="D273" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E273" t="s">
         <v>10</v>
       </c>
       <c r="F273">
-        <v>102</v>
+        <v>125</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -8954,19 +8966,19 @@
         <v>564</v>
       </c>
       <c r="B274" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C274" t="s">
         <v>565</v>
       </c>
       <c r="D274" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E274" t="s">
         <v>10</v>
       </c>
       <c r="F274">
-        <v>171</v>
+        <v>215</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -8974,39 +8986,39 @@
         <v>566</v>
       </c>
       <c r="B275" t="s">
-        <v>530</v>
+        <v>567</v>
       </c>
       <c r="C275" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D275" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E275" t="s">
         <v>10</v>
       </c>
       <c r="F275">
-        <v>183</v>
+        <v>153</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B276" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C276" t="s">
         <v>570</v>
       </c>
       <c r="D276" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E276" t="s">
         <v>10</v>
       </c>
       <c r="F276">
-        <v>257</v>
+        <v>136</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -9014,7 +9026,7 @@
         <v>571</v>
       </c>
       <c r="B277" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C277" t="s">
         <v>572</v>
@@ -9026,7 +9038,7 @@
         <v>10</v>
       </c>
       <c r="F277">
-        <v>164</v>
+        <v>251</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -9034,7 +9046,7 @@
         <v>573</v>
       </c>
       <c r="B278" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C278" t="s">
         <v>574</v>
@@ -9046,7 +9058,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>199</v>
+        <v>275</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -9054,7 +9066,7 @@
         <v>575</v>
       </c>
       <c r="B279" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C279" t="s">
         <v>576</v>
@@ -9066,7 +9078,7 @@
         <v>10</v>
       </c>
       <c r="F279">
-        <v>238</v>
+        <v>160</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -9074,7 +9086,7 @@
         <v>577</v>
       </c>
       <c r="B280" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C280" t="s">
         <v>578</v>
@@ -9086,7 +9098,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>168</v>
+        <v>131</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -9094,7 +9106,7 @@
         <v>579</v>
       </c>
       <c r="B281" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C281" t="s">
         <v>580</v>
@@ -9106,7 +9118,7 @@
         <v>10</v>
       </c>
       <c r="F281">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -9114,7 +9126,7 @@
         <v>581</v>
       </c>
       <c r="B282" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C282" t="s">
         <v>582</v>
@@ -9126,7 +9138,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>109</v>
+        <v>277</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -9134,7 +9146,7 @@
         <v>583</v>
       </c>
       <c r="B283" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C283" t="s">
         <v>584</v>
@@ -9146,7 +9158,7 @@
         <v>10</v>
       </c>
       <c r="F283">
-        <v>264</v>
+        <v>127</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -9154,7 +9166,7 @@
         <v>585</v>
       </c>
       <c r="B284" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C284" t="s">
         <v>586</v>
@@ -9166,7 +9178,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>218</v>
+        <v>201</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -9174,7 +9186,7 @@
         <v>587</v>
       </c>
       <c r="B285" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C285" t="s">
         <v>588</v>
@@ -9186,7 +9198,7 @@
         <v>10</v>
       </c>
       <c r="F285">
-        <v>294</v>
+        <v>169</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -9194,7 +9206,7 @@
         <v>589</v>
       </c>
       <c r="B286" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C286" t="s">
         <v>590</v>
@@ -9206,7 +9218,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>282</v>
+        <v>268</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -9214,7 +9226,7 @@
         <v>591</v>
       </c>
       <c r="B287" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C287" t="s">
         <v>592</v>
@@ -9226,7 +9238,7 @@
         <v>10</v>
       </c>
       <c r="F287">
-        <v>190</v>
+        <v>101</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -9234,7 +9246,7 @@
         <v>593</v>
       </c>
       <c r="B288" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C288" t="s">
         <v>594</v>
@@ -9246,7 +9258,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>295</v>
+        <v>166</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -9254,7 +9266,7 @@
         <v>595</v>
       </c>
       <c r="B289" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C289" t="s">
         <v>596</v>
@@ -9266,7 +9278,7 @@
         <v>10</v>
       </c>
       <c r="F289">
-        <v>201</v>
+        <v>127</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -9274,7 +9286,7 @@
         <v>597</v>
       </c>
       <c r="B290" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C290" t="s">
         <v>598</v>
@@ -9286,7 +9298,7 @@
         <v>10</v>
       </c>
       <c r="F290">
-        <v>236</v>
+        <v>279</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -9294,7 +9306,7 @@
         <v>599</v>
       </c>
       <c r="B291" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C291" t="s">
         <v>600</v>
@@ -9306,7 +9318,7 @@
         <v>10</v>
       </c>
       <c r="F291">
-        <v>212</v>
+        <v>234</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -9314,7 +9326,7 @@
         <v>601</v>
       </c>
       <c r="B292" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C292" t="s">
         <v>602</v>
@@ -9326,7 +9338,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>271</v>
+        <v>282</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -9334,7 +9346,7 @@
         <v>603</v>
       </c>
       <c r="B293" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C293" t="s">
         <v>604</v>
@@ -9346,7 +9358,7 @@
         <v>10</v>
       </c>
       <c r="F293">
-        <v>229</v>
+        <v>118</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -9354,7 +9366,7 @@
         <v>605</v>
       </c>
       <c r="B294" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C294" t="s">
         <v>606</v>
@@ -9366,7 +9378,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>245</v>
+        <v>287</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -9374,7 +9386,7 @@
         <v>607</v>
       </c>
       <c r="B295" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C295" t="s">
         <v>608</v>
@@ -9386,7 +9398,7 @@
         <v>10</v>
       </c>
       <c r="F295">
-        <v>240</v>
+        <v>224</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -9394,7 +9406,7 @@
         <v>609</v>
       </c>
       <c r="B296" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C296" t="s">
         <v>610</v>
@@ -9406,7 +9418,7 @@
         <v>10</v>
       </c>
       <c r="F296">
-        <v>135</v>
+        <v>280</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -9414,7 +9426,7 @@
         <v>611</v>
       </c>
       <c r="B297" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C297" t="s">
         <v>612</v>
@@ -9426,7 +9438,7 @@
         <v>10</v>
       </c>
       <c r="F297">
-        <v>295</v>
+        <v>197</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -9434,7 +9446,7 @@
         <v>613</v>
       </c>
       <c r="B298" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C298" t="s">
         <v>614</v>
@@ -9446,7 +9458,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>137</v>
+        <v>173</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -9454,7 +9466,7 @@
         <v>615</v>
       </c>
       <c r="B299" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C299" t="s">
         <v>616</v>
@@ -9466,7 +9478,7 @@
         <v>10</v>
       </c>
       <c r="F299">
-        <v>137</v>
+        <v>297</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -9474,7 +9486,7 @@
         <v>617</v>
       </c>
       <c r="B300" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C300" t="s">
         <v>618</v>
@@ -9486,7 +9498,7 @@
         <v>10</v>
       </c>
       <c r="F300">
-        <v>140</v>
+        <v>296</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -9494,7 +9506,7 @@
         <v>619</v>
       </c>
       <c r="B301" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C301" t="s">
         <v>620</v>
@@ -9506,7 +9518,7 @@
         <v>10</v>
       </c>
       <c r="F301">
-        <v>216</v>
+        <v>289</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -9514,7 +9526,7 @@
         <v>621</v>
       </c>
       <c r="B302" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C302" t="s">
         <v>622</v>
@@ -9526,7 +9538,7 @@
         <v>10</v>
       </c>
       <c r="F302">
-        <v>121</v>
+        <v>244</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -9534,7 +9546,7 @@
         <v>623</v>
       </c>
       <c r="B303" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C303" t="s">
         <v>624</v>
@@ -9546,7 +9558,7 @@
         <v>10</v>
       </c>
       <c r="F303">
-        <v>158</v>
+        <v>275</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -9554,7 +9566,7 @@
         <v>625</v>
       </c>
       <c r="B304" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C304" t="s">
         <v>626</v>
@@ -9566,7 +9578,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>239</v>
+        <v>142</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -9574,7 +9586,7 @@
         <v>627</v>
       </c>
       <c r="B305" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C305" t="s">
         <v>628</v>
@@ -9586,7 +9598,7 @@
         <v>10</v>
       </c>
       <c r="F305">
-        <v>140</v>
+        <v>299</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -9594,7 +9606,7 @@
         <v>629</v>
       </c>
       <c r="B306" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C306" t="s">
         <v>630</v>
@@ -9606,7 +9618,7 @@
         <v>10</v>
       </c>
       <c r="F306">
-        <v>114</v>
+        <v>221</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -9614,7 +9626,7 @@
         <v>631</v>
       </c>
       <c r="B307" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C307" t="s">
         <v>632</v>
@@ -9626,7 +9638,7 @@
         <v>10</v>
       </c>
       <c r="F307">
-        <v>248</v>
+        <v>283</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -9634,7 +9646,7 @@
         <v>633</v>
       </c>
       <c r="B308" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C308" t="s">
         <v>634</v>
@@ -9646,7 +9658,7 @@
         <v>10</v>
       </c>
       <c r="F308">
-        <v>156</v>
+        <v>257</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -9654,7 +9666,7 @@
         <v>635</v>
       </c>
       <c r="B309" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C309" t="s">
         <v>636</v>
@@ -9666,7 +9678,7 @@
         <v>10</v>
       </c>
       <c r="F309">
-        <v>168</v>
+        <v>212</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -9674,7 +9686,7 @@
         <v>637</v>
       </c>
       <c r="B310" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C310" t="s">
         <v>638</v>
@@ -9686,7 +9698,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>261</v>
+        <v>210</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -9694,7 +9706,7 @@
         <v>639</v>
       </c>
       <c r="B311" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C311" t="s">
         <v>640</v>
@@ -9706,7 +9718,7 @@
         <v>10</v>
       </c>
       <c r="F311">
-        <v>168</v>
+        <v>299</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -9714,7 +9726,7 @@
         <v>641</v>
       </c>
       <c r="B312" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C312" t="s">
         <v>642</v>
@@ -9726,7 +9738,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>157</v>
+        <v>276</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -9734,7 +9746,7 @@
         <v>643</v>
       </c>
       <c r="B313" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C313" t="s">
         <v>644</v>
@@ -9746,7 +9758,7 @@
         <v>10</v>
       </c>
       <c r="F313">
-        <v>216</v>
+        <v>282</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -9754,7 +9766,7 @@
         <v>645</v>
       </c>
       <c r="B314" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C314" t="s">
         <v>646</v>
@@ -9766,7 +9778,7 @@
         <v>10</v>
       </c>
       <c r="F314">
-        <v>116</v>
+        <v>142</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -9786,7 +9798,7 @@
         <v>10</v>
       </c>
       <c r="F315">
-        <v>267</v>
+        <v>101</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -9806,7 +9818,7 @@
         <v>10</v>
       </c>
       <c r="F316">
-        <v>276</v>
+        <v>222</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -9826,7 +9838,7 @@
         <v>10</v>
       </c>
       <c r="F317">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -9846,7 +9858,7 @@
         <v>10</v>
       </c>
       <c r="F318">
-        <v>214</v>
+        <v>200</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -9866,7 +9878,7 @@
         <v>10</v>
       </c>
       <c r="F319">
-        <v>293</v>
+        <v>224</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -9886,7 +9898,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>113</v>
+        <v>288</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -9906,7 +9918,7 @@
         <v>10</v>
       </c>
       <c r="F321">
-        <v>169</v>
+        <v>266</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -9926,7 +9938,7 @@
         <v>10</v>
       </c>
       <c r="F322">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -9940,13 +9952,13 @@
         <v>665</v>
       </c>
       <c r="D323" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E323" t="s">
         <v>10</v>
       </c>
       <c r="F323">
-        <v>192</v>
+        <v>164</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -9960,13 +9972,13 @@
         <v>667</v>
       </c>
       <c r="D324" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E324" t="s">
         <v>10</v>
       </c>
       <c r="F324">
-        <v>283</v>
+        <v>163</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -9980,13 +9992,13 @@
         <v>669</v>
       </c>
       <c r="D325" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E325" t="s">
         <v>10</v>
       </c>
       <c r="F325">
-        <v>242</v>
+        <v>208</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -10000,13 +10012,13 @@
         <v>671</v>
       </c>
       <c r="D326" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E326" t="s">
         <v>10</v>
       </c>
       <c r="F326">
-        <v>280</v>
+        <v>271</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -10020,13 +10032,13 @@
         <v>673</v>
       </c>
       <c r="D327" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E327" t="s">
         <v>10</v>
       </c>
       <c r="F327">
-        <v>299</v>
+        <v>178</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -10040,13 +10052,13 @@
         <v>675</v>
       </c>
       <c r="D328" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E328" t="s">
         <v>10</v>
       </c>
       <c r="F328">
-        <v>198</v>
+        <v>293</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -10060,13 +10072,13 @@
         <v>677</v>
       </c>
       <c r="D329" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E329" t="s">
         <v>10</v>
       </c>
       <c r="F329">
-        <v>130</v>
+        <v>268</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -10080,13 +10092,13 @@
         <v>679</v>
       </c>
       <c r="D330" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E330" t="s">
         <v>10</v>
       </c>
       <c r="F330">
-        <v>266</v>
+        <v>166</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -10100,13 +10112,13 @@
         <v>681</v>
       </c>
       <c r="D331" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E331" t="s">
         <v>10</v>
       </c>
       <c r="F331">
-        <v>171</v>
+        <v>287</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -10120,13 +10132,13 @@
         <v>683</v>
       </c>
       <c r="D332" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E332" t="s">
         <v>10</v>
       </c>
       <c r="F332">
-        <v>132</v>
+        <v>263</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -10140,13 +10152,13 @@
         <v>685</v>
       </c>
       <c r="D333" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E333" t="s">
         <v>10</v>
       </c>
       <c r="F333">
-        <v>263</v>
+        <v>226</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -10154,39 +10166,39 @@
         <v>686</v>
       </c>
       <c r="B334" t="s">
-        <v>648</v>
+        <v>687</v>
       </c>
       <c r="C334" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D334" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E334" t="s">
         <v>10</v>
       </c>
       <c r="F334">
-        <v>228</v>
+        <v>113</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B335" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C335" t="s">
         <v>690</v>
       </c>
       <c r="D335" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E335" t="s">
         <v>10</v>
       </c>
       <c r="F335">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -10194,19 +10206,19 @@
         <v>691</v>
       </c>
       <c r="B336" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C336" t="s">
         <v>692</v>
       </c>
       <c r="D336" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E336" t="s">
         <v>10</v>
       </c>
       <c r="F336">
-        <v>267</v>
+        <v>189</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -10214,19 +10226,19 @@
         <v>693</v>
       </c>
       <c r="B337" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C337" t="s">
         <v>694</v>
       </c>
       <c r="D337" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E337" t="s">
         <v>10</v>
       </c>
       <c r="F337">
-        <v>153</v>
+        <v>238</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -10234,19 +10246,19 @@
         <v>695</v>
       </c>
       <c r="B338" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C338" t="s">
         <v>696</v>
       </c>
       <c r="D338" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E338" t="s">
         <v>10</v>
       </c>
       <c r="F338">
-        <v>153</v>
+        <v>175</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -10254,19 +10266,19 @@
         <v>697</v>
       </c>
       <c r="B339" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C339" t="s">
         <v>698</v>
       </c>
       <c r="D339" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E339" t="s">
         <v>10</v>
       </c>
       <c r="F339">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -10274,19 +10286,19 @@
         <v>699</v>
       </c>
       <c r="B340" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C340" t="s">
         <v>700</v>
       </c>
       <c r="D340" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E340" t="s">
         <v>10</v>
       </c>
       <c r="F340">
-        <v>199</v>
+        <v>141</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -10294,19 +10306,19 @@
         <v>701</v>
       </c>
       <c r="B341" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C341" t="s">
         <v>702</v>
       </c>
       <c r="D341" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E341" t="s">
         <v>10</v>
       </c>
       <c r="F341">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -10314,19 +10326,19 @@
         <v>703</v>
       </c>
       <c r="B342" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C342" t="s">
         <v>704</v>
       </c>
       <c r="D342" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E342" t="s">
         <v>10</v>
       </c>
       <c r="F342">
-        <v>134</v>
+        <v>299</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -10334,19 +10346,19 @@
         <v>705</v>
       </c>
       <c r="B343" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C343" t="s">
         <v>706</v>
       </c>
       <c r="D343" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E343" t="s">
         <v>10</v>
       </c>
       <c r="F343">
-        <v>218</v>
+        <v>263</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -10354,19 +10366,19 @@
         <v>707</v>
       </c>
       <c r="B344" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C344" t="s">
         <v>708</v>
       </c>
       <c r="D344" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E344" t="s">
         <v>10</v>
       </c>
       <c r="F344">
-        <v>253</v>
+        <v>165</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -10374,19 +10386,19 @@
         <v>709</v>
       </c>
       <c r="B345" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C345" t="s">
         <v>710</v>
       </c>
       <c r="D345" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E345" t="s">
         <v>10</v>
       </c>
       <c r="F345">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -10394,19 +10406,19 @@
         <v>711</v>
       </c>
       <c r="B346" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C346" t="s">
         <v>712</v>
       </c>
       <c r="D346" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E346" t="s">
         <v>10</v>
       </c>
       <c r="F346">
-        <v>283</v>
+        <v>128</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -10414,19 +10426,19 @@
         <v>713</v>
       </c>
       <c r="B347" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C347" t="s">
         <v>714</v>
       </c>
       <c r="D347" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E347" t="s">
         <v>10</v>
       </c>
       <c r="F347">
-        <v>148</v>
+        <v>197</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -10434,19 +10446,19 @@
         <v>715</v>
       </c>
       <c r="B348" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C348" t="s">
         <v>716</v>
       </c>
       <c r="D348" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E348" t="s">
         <v>10</v>
       </c>
       <c r="F348">
-        <v>173</v>
+        <v>194</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -10454,19 +10466,19 @@
         <v>717</v>
       </c>
       <c r="B349" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C349" t="s">
         <v>718</v>
       </c>
       <c r="D349" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E349" t="s">
         <v>10</v>
       </c>
       <c r="F349">
-        <v>210</v>
+        <v>140</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -10474,19 +10486,19 @@
         <v>719</v>
       </c>
       <c r="B350" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C350" t="s">
         <v>720</v>
       </c>
       <c r="D350" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E350" t="s">
         <v>10</v>
       </c>
       <c r="F350">
-        <v>231</v>
+        <v>169</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -10494,19 +10506,19 @@
         <v>721</v>
       </c>
       <c r="B351" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C351" t="s">
         <v>722</v>
       </c>
       <c r="D351" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E351" t="s">
         <v>10</v>
       </c>
       <c r="F351">
-        <v>158</v>
+        <v>240</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -10514,19 +10526,19 @@
         <v>723</v>
       </c>
       <c r="B352" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C352" t="s">
         <v>724</v>
       </c>
       <c r="D352" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E352" t="s">
         <v>10</v>
       </c>
       <c r="F352">
-        <v>263</v>
+        <v>242</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -10534,10 +10546,10 @@
         <v>725</v>
       </c>
       <c r="B353" t="s">
-        <v>689</v>
+        <v>726</v>
       </c>
       <c r="C353" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D353" t="s">
         <v>9</v>
@@ -10546,18 +10558,18 @@
         <v>10</v>
       </c>
       <c r="F353">
-        <v>141</v>
+        <v>289</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B354" t="s">
-        <v>689</v>
+        <v>726</v>
       </c>
       <c r="C354" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D354" t="s">
         <v>13</v>
@@ -10566,27 +10578,27 @@
         <v>10</v>
       </c>
       <c r="F354">
-        <v>254</v>
+        <v>225</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B355" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C355" t="s">
         <v>731</v>
       </c>
       <c r="D355" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E355" t="s">
         <v>10</v>
       </c>
       <c r="F355">
-        <v>276</v>
+        <v>236</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -10594,19 +10606,19 @@
         <v>732</v>
       </c>
       <c r="B356" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C356" t="s">
         <v>733</v>
       </c>
       <c r="D356" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E356" t="s">
         <v>10</v>
       </c>
       <c r="F356">
-        <v>294</v>
+        <v>185</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -10614,19 +10626,19 @@
         <v>734</v>
       </c>
       <c r="B357" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C357" t="s">
         <v>735</v>
       </c>
       <c r="D357" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E357" t="s">
         <v>10</v>
       </c>
       <c r="F357">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -10634,19 +10646,19 @@
         <v>736</v>
       </c>
       <c r="B358" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C358" t="s">
         <v>737</v>
       </c>
       <c r="D358" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E358" t="s">
         <v>10</v>
       </c>
       <c r="F358">
-        <v>272</v>
+        <v>231</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -10654,19 +10666,19 @@
         <v>738</v>
       </c>
       <c r="B359" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C359" t="s">
         <v>739</v>
       </c>
       <c r="D359" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E359" t="s">
         <v>10</v>
       </c>
       <c r="F359">
-        <v>295</v>
+        <v>212</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -10674,19 +10686,19 @@
         <v>740</v>
       </c>
       <c r="B360" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C360" t="s">
         <v>741</v>
       </c>
       <c r="D360" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E360" t="s">
         <v>10</v>
       </c>
       <c r="F360">
-        <v>157</v>
+        <v>118</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -10694,19 +10706,19 @@
         <v>742</v>
       </c>
       <c r="B361" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C361" t="s">
         <v>743</v>
       </c>
       <c r="D361" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E361" t="s">
         <v>10</v>
       </c>
       <c r="F361">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -10714,19 +10726,19 @@
         <v>744</v>
       </c>
       <c r="B362" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C362" t="s">
         <v>745</v>
       </c>
       <c r="D362" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E362" t="s">
         <v>10</v>
       </c>
       <c r="F362">
-        <v>159</v>
+        <v>202</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -10734,19 +10746,19 @@
         <v>746</v>
       </c>
       <c r="B363" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C363" t="s">
         <v>747</v>
       </c>
       <c r="D363" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E363" t="s">
         <v>10</v>
       </c>
       <c r="F363">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -10754,19 +10766,19 @@
         <v>748</v>
       </c>
       <c r="B364" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C364" t="s">
         <v>749</v>
       </c>
       <c r="D364" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E364" t="s">
         <v>10</v>
       </c>
       <c r="F364">
-        <v>196</v>
+        <v>169</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -10774,19 +10786,19 @@
         <v>750</v>
       </c>
       <c r="B365" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C365" t="s">
         <v>751</v>
       </c>
       <c r="D365" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E365" t="s">
         <v>10</v>
       </c>
       <c r="F365">
-        <v>106</v>
+        <v>172</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -10794,19 +10806,19 @@
         <v>752</v>
       </c>
       <c r="B366" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C366" t="s">
         <v>753</v>
       </c>
       <c r="D366" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E366" t="s">
         <v>10</v>
       </c>
       <c r="F366">
-        <v>168</v>
+        <v>124</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -10814,19 +10826,19 @@
         <v>754</v>
       </c>
       <c r="B367" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C367" t="s">
         <v>755</v>
       </c>
       <c r="D367" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E367" t="s">
         <v>10</v>
       </c>
       <c r="F367">
-        <v>276</v>
+        <v>255</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -10834,19 +10846,19 @@
         <v>756</v>
       </c>
       <c r="B368" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C368" t="s">
         <v>757</v>
       </c>
       <c r="D368" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E368" t="s">
         <v>10</v>
       </c>
       <c r="F368">
-        <v>143</v>
+        <v>277</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -10854,19 +10866,19 @@
         <v>758</v>
       </c>
       <c r="B369" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C369" t="s">
         <v>759</v>
       </c>
       <c r="D369" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E369" t="s">
         <v>10</v>
       </c>
       <c r="F369">
-        <v>158</v>
+        <v>106</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -10874,19 +10886,19 @@
         <v>760</v>
       </c>
       <c r="B370" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C370" t="s">
         <v>761</v>
       </c>
       <c r="D370" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E370" t="s">
         <v>10</v>
       </c>
       <c r="F370">
-        <v>158</v>
+        <v>126</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -10894,19 +10906,19 @@
         <v>762</v>
       </c>
       <c r="B371" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C371" t="s">
         <v>763</v>
       </c>
       <c r="D371" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E371" t="s">
         <v>10</v>
       </c>
       <c r="F371">
-        <v>175</v>
+        <v>289</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -10914,19 +10926,19 @@
         <v>764</v>
       </c>
       <c r="B372" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C372" t="s">
         <v>765</v>
       </c>
       <c r="D372" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E372" t="s">
         <v>10</v>
       </c>
       <c r="F372">
-        <v>209</v>
+        <v>133</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -10934,39 +10946,39 @@
         <v>766</v>
       </c>
       <c r="B373" t="s">
-        <v>730</v>
+        <v>767</v>
       </c>
       <c r="C373" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D373" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E373" t="s">
         <v>10</v>
       </c>
       <c r="F373">
-        <v>139</v>
+        <v>247</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B374" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C374" t="s">
         <v>770</v>
       </c>
       <c r="D374" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E374" t="s">
         <v>10</v>
       </c>
       <c r="F374">
-        <v>208</v>
+        <v>252</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -10974,19 +10986,19 @@
         <v>771</v>
       </c>
       <c r="B375" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C375" t="s">
         <v>772</v>
       </c>
       <c r="D375" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E375" t="s">
         <v>10</v>
       </c>
       <c r="F375">
-        <v>213</v>
+        <v>245</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -10994,19 +11006,19 @@
         <v>773</v>
       </c>
       <c r="B376" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C376" t="s">
         <v>774</v>
       </c>
       <c r="D376" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E376" t="s">
         <v>10</v>
       </c>
       <c r="F376">
-        <v>215</v>
+        <v>116</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -11014,19 +11026,19 @@
         <v>775</v>
       </c>
       <c r="B377" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C377" t="s">
         <v>776</v>
       </c>
       <c r="D377" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E377" t="s">
         <v>10</v>
       </c>
       <c r="F377">
-        <v>275</v>
+        <v>263</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -11034,19 +11046,19 @@
         <v>777</v>
       </c>
       <c r="B378" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C378" t="s">
         <v>778</v>
       </c>
       <c r="D378" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E378" t="s">
         <v>10</v>
       </c>
       <c r="F378">
-        <v>200</v>
+        <v>159</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -11054,19 +11066,19 @@
         <v>779</v>
       </c>
       <c r="B379" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C379" t="s">
         <v>780</v>
       </c>
       <c r="D379" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E379" t="s">
         <v>10</v>
       </c>
       <c r="F379">
-        <v>168</v>
+        <v>177</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -11074,19 +11086,19 @@
         <v>781</v>
       </c>
       <c r="B380" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C380" t="s">
         <v>782</v>
       </c>
       <c r="D380" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E380" t="s">
         <v>10</v>
       </c>
       <c r="F380">
-        <v>132</v>
+        <v>116</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -11094,19 +11106,19 @@
         <v>783</v>
       </c>
       <c r="B381" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C381" t="s">
         <v>784</v>
       </c>
       <c r="D381" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E381" t="s">
         <v>10</v>
       </c>
       <c r="F381">
-        <v>136</v>
+        <v>103</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -11114,19 +11126,19 @@
         <v>785</v>
       </c>
       <c r="B382" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C382" t="s">
         <v>786</v>
       </c>
       <c r="D382" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E382" t="s">
         <v>10</v>
       </c>
       <c r="F382">
-        <v>233</v>
+        <v>284</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -11134,19 +11146,19 @@
         <v>787</v>
       </c>
       <c r="B383" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C383" t="s">
         <v>788</v>
       </c>
       <c r="D383" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E383" t="s">
         <v>10</v>
       </c>
       <c r="F383">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -11154,19 +11166,19 @@
         <v>789</v>
       </c>
       <c r="B384" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C384" t="s">
         <v>790</v>
       </c>
       <c r="D384" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E384" t="s">
         <v>10</v>
       </c>
       <c r="F384">
-        <v>196</v>
+        <v>171</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -11174,19 +11186,19 @@
         <v>791</v>
       </c>
       <c r="B385" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C385" t="s">
         <v>792</v>
       </c>
       <c r="D385" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E385" t="s">
         <v>10</v>
       </c>
       <c r="F385">
-        <v>150</v>
+        <v>289</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -11194,19 +11206,19 @@
         <v>793</v>
       </c>
       <c r="B386" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C386" t="s">
         <v>794</v>
       </c>
       <c r="D386" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E386" t="s">
         <v>10</v>
       </c>
       <c r="F386">
-        <v>108</v>
+        <v>200</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -11214,19 +11226,19 @@
         <v>795</v>
       </c>
       <c r="B387" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C387" t="s">
         <v>796</v>
       </c>
       <c r="D387" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E387" t="s">
         <v>10</v>
       </c>
       <c r="F387">
-        <v>277</v>
+        <v>156</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -11234,19 +11246,19 @@
         <v>797</v>
       </c>
       <c r="B388" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C388" t="s">
         <v>798</v>
       </c>
       <c r="D388" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E388" t="s">
         <v>10</v>
       </c>
       <c r="F388">
-        <v>200</v>
+        <v>223</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -11254,19 +11266,19 @@
         <v>799</v>
       </c>
       <c r="B389" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C389" t="s">
         <v>800</v>
       </c>
       <c r="D389" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E389" t="s">
         <v>10</v>
       </c>
       <c r="F389">
-        <v>259</v>
+        <v>124</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -11274,19 +11286,19 @@
         <v>801</v>
       </c>
       <c r="B390" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C390" t="s">
         <v>802</v>
       </c>
       <c r="D390" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E390" t="s">
         <v>10</v>
       </c>
       <c r="F390">
-        <v>253</v>
+        <v>100</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -11294,19 +11306,19 @@
         <v>803</v>
       </c>
       <c r="B391" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C391" t="s">
         <v>804</v>
       </c>
       <c r="D391" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E391" t="s">
         <v>10</v>
       </c>
       <c r="F391">
-        <v>107</v>
+        <v>200</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -11314,10 +11326,10 @@
         <v>805</v>
       </c>
       <c r="B392" t="s">
-        <v>769</v>
+        <v>806</v>
       </c>
       <c r="C392" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D392" t="s">
         <v>9</v>
@@ -11326,18 +11338,18 @@
         <v>10</v>
       </c>
       <c r="F392">
-        <v>136</v>
+        <v>276</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B393" t="s">
-        <v>769</v>
+        <v>806</v>
       </c>
       <c r="C393" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D393" t="s">
         <v>13</v>
@@ -11346,27 +11358,27 @@
         <v>10</v>
       </c>
       <c r="F393">
-        <v>180</v>
+        <v>117</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B394" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C394" t="s">
         <v>811</v>
       </c>
       <c r="D394" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E394" t="s">
         <v>10</v>
       </c>
       <c r="F394">
-        <v>273</v>
+        <v>208</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -11374,19 +11386,19 @@
         <v>812</v>
       </c>
       <c r="B395" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C395" t="s">
         <v>813</v>
       </c>
       <c r="D395" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E395" t="s">
         <v>10</v>
       </c>
       <c r="F395">
-        <v>107</v>
+        <v>138</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -11394,19 +11406,19 @@
         <v>814</v>
       </c>
       <c r="B396" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C396" t="s">
         <v>815</v>
       </c>
       <c r="D396" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E396" t="s">
         <v>10</v>
       </c>
       <c r="F396">
-        <v>224</v>
+        <v>280</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -11414,19 +11426,19 @@
         <v>816</v>
       </c>
       <c r="B397" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C397" t="s">
         <v>817</v>
       </c>
       <c r="D397" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E397" t="s">
         <v>10</v>
       </c>
       <c r="F397">
-        <v>287</v>
+        <v>132</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -11434,19 +11446,19 @@
         <v>818</v>
       </c>
       <c r="B398" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C398" t="s">
         <v>819</v>
       </c>
       <c r="D398" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E398" t="s">
         <v>10</v>
       </c>
       <c r="F398">
-        <v>202</v>
+        <v>145</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -11454,19 +11466,19 @@
         <v>820</v>
       </c>
       <c r="B399" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C399" t="s">
         <v>821</v>
       </c>
       <c r="D399" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E399" t="s">
         <v>10</v>
       </c>
       <c r="F399">
-        <v>125</v>
+        <v>207</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -11474,19 +11486,19 @@
         <v>822</v>
       </c>
       <c r="B400" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C400" t="s">
         <v>823</v>
       </c>
       <c r="D400" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E400" t="s">
         <v>10</v>
       </c>
       <c r="F400">
-        <v>114</v>
+        <v>213</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -11494,19 +11506,19 @@
         <v>824</v>
       </c>
       <c r="B401" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C401" t="s">
         <v>825</v>
       </c>
       <c r="D401" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E401" t="s">
         <v>10</v>
       </c>
       <c r="F401">
-        <v>251</v>
+        <v>273</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -11514,59 +11526,59 @@
         <v>826</v>
       </c>
       <c r="B402" t="s">
-        <v>810</v>
+        <v>827</v>
       </c>
       <c r="C402" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D402" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E402" t="s">
         <v>10</v>
       </c>
       <c r="F402">
-        <v>201</v>
+        <v>133</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B403" t="s">
-        <v>810</v>
+        <v>827</v>
       </c>
       <c r="C403" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D403" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E403" t="s">
         <v>10</v>
       </c>
       <c r="F403">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B404" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C404" t="s">
         <v>832</v>
       </c>
       <c r="D404" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E404" t="s">
         <v>10</v>
       </c>
       <c r="F404">
-        <v>102</v>
+        <v>230</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -11574,19 +11586,19 @@
         <v>833</v>
       </c>
       <c r="B405" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C405" t="s">
         <v>834</v>
       </c>
       <c r="D405" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E405" t="s">
         <v>10</v>
       </c>
       <c r="F405">
-        <v>199</v>
+        <v>217</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -11594,19 +11606,19 @@
         <v>835</v>
       </c>
       <c r="B406" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C406" t="s">
         <v>836</v>
       </c>
       <c r="D406" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E406" t="s">
         <v>10</v>
       </c>
       <c r="F406">
-        <v>155</v>
+        <v>109</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -11614,19 +11626,19 @@
         <v>837</v>
       </c>
       <c r="B407" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C407" t="s">
         <v>838</v>
       </c>
       <c r="D407" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E407" t="s">
         <v>10</v>
       </c>
       <c r="F407">
-        <v>155</v>
+        <v>121</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -11634,19 +11646,19 @@
         <v>839</v>
       </c>
       <c r="B408" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C408" t="s">
         <v>840</v>
       </c>
       <c r="D408" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E408" t="s">
         <v>10</v>
       </c>
       <c r="F408">
-        <v>121</v>
+        <v>265</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -11654,19 +11666,19 @@
         <v>841</v>
       </c>
       <c r="B409" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C409" t="s">
         <v>842</v>
       </c>
       <c r="D409" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E409" t="s">
         <v>10</v>
       </c>
       <c r="F409">
-        <v>152</v>
+        <v>234</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -11674,19 +11686,19 @@
         <v>843</v>
       </c>
       <c r="B410" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C410" t="s">
         <v>844</v>
       </c>
       <c r="D410" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E410" t="s">
         <v>10</v>
       </c>
       <c r="F410">
-        <v>215</v>
+        <v>175</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -11694,19 +11706,19 @@
         <v>845</v>
       </c>
       <c r="B411" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C411" t="s">
         <v>846</v>
       </c>
       <c r="D411" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E411" t="s">
         <v>10</v>
       </c>
       <c r="F411">
-        <v>299</v>
+        <v>214</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -11714,19 +11726,19 @@
         <v>847</v>
       </c>
       <c r="B412" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C412" t="s">
         <v>848</v>
       </c>
       <c r="D412" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E412" t="s">
         <v>10</v>
       </c>
       <c r="F412">
-        <v>138</v>
+        <v>294</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -11734,19 +11746,19 @@
         <v>849</v>
       </c>
       <c r="B413" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C413" t="s">
         <v>850</v>
       </c>
       <c r="D413" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E413" t="s">
         <v>10</v>
       </c>
       <c r="F413">
-        <v>128</v>
+        <v>210</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -11754,19 +11766,19 @@
         <v>851</v>
       </c>
       <c r="B414" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C414" t="s">
         <v>852</v>
       </c>
       <c r="D414" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E414" t="s">
         <v>10</v>
       </c>
       <c r="F414">
-        <v>151</v>
+        <v>263</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -11774,19 +11786,19 @@
         <v>853</v>
       </c>
       <c r="B415" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C415" t="s">
         <v>854</v>
       </c>
       <c r="D415" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E415" t="s">
         <v>10</v>
       </c>
       <c r="F415">
-        <v>247</v>
+        <v>155</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -11794,19 +11806,19 @@
         <v>855</v>
       </c>
       <c r="B416" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C416" t="s">
         <v>856</v>
       </c>
       <c r="D416" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E416" t="s">
         <v>10</v>
       </c>
       <c r="F416">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -11814,19 +11826,19 @@
         <v>857</v>
       </c>
       <c r="B417" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C417" t="s">
         <v>858</v>
       </c>
       <c r="D417" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E417" t="s">
         <v>10</v>
       </c>
       <c r="F417">
-        <v>138</v>
+        <v>155</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -11834,19 +11846,19 @@
         <v>859</v>
       </c>
       <c r="B418" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C418" t="s">
         <v>860</v>
       </c>
       <c r="D418" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E418" t="s">
         <v>10</v>
       </c>
       <c r="F418">
-        <v>122</v>
+        <v>179</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -11854,19 +11866,19 @@
         <v>861</v>
       </c>
       <c r="B419" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C419" t="s">
         <v>862</v>
       </c>
       <c r="D419" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E419" t="s">
         <v>10</v>
       </c>
       <c r="F419">
-        <v>143</v>
+        <v>231</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -11874,19 +11886,19 @@
         <v>863</v>
       </c>
       <c r="B420" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C420" t="s">
         <v>864</v>
       </c>
       <c r="D420" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E420" t="s">
         <v>10</v>
       </c>
       <c r="F420">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -11894,19 +11906,19 @@
         <v>865</v>
       </c>
       <c r="B421" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C421" t="s">
         <v>866</v>
       </c>
       <c r="D421" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E421" t="s">
         <v>10</v>
       </c>
       <c r="F421">
-        <v>253</v>
+        <v>282</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -11914,39 +11926,39 @@
         <v>867</v>
       </c>
       <c r="B422" t="s">
-        <v>831</v>
+        <v>868</v>
       </c>
       <c r="C422" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D422" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E422" t="s">
         <v>10</v>
       </c>
       <c r="F422">
-        <v>131</v>
+        <v>228</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B423" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C423" t="s">
         <v>871</v>
       </c>
       <c r="D423" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E423" t="s">
         <v>10</v>
       </c>
       <c r="F423">
-        <v>215</v>
+        <v>181</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -11954,19 +11966,19 @@
         <v>872</v>
       </c>
       <c r="B424" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C424" t="s">
         <v>873</v>
       </c>
       <c r="D424" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E424" t="s">
         <v>10</v>
       </c>
       <c r="F424">
-        <v>174</v>
+        <v>263</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -11974,19 +11986,19 @@
         <v>874</v>
       </c>
       <c r="B425" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C425" t="s">
         <v>875</v>
       </c>
       <c r="D425" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E425" t="s">
         <v>10</v>
       </c>
       <c r="F425">
-        <v>160</v>
+        <v>114</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -11994,19 +12006,19 @@
         <v>876</v>
       </c>
       <c r="B426" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C426" t="s">
         <v>877</v>
       </c>
       <c r="D426" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E426" t="s">
         <v>10</v>
       </c>
       <c r="F426">
-        <v>248</v>
+        <v>274</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -12014,19 +12026,19 @@
         <v>878</v>
       </c>
       <c r="B427" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C427" t="s">
         <v>879</v>
       </c>
       <c r="D427" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E427" t="s">
         <v>10</v>
       </c>
       <c r="F427">
-        <v>228</v>
+        <v>145</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -12034,19 +12046,19 @@
         <v>880</v>
       </c>
       <c r="B428" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C428" t="s">
         <v>881</v>
       </c>
       <c r="D428" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E428" t="s">
         <v>10</v>
       </c>
       <c r="F428">
-        <v>258</v>
+        <v>175</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -12054,19 +12066,19 @@
         <v>882</v>
       </c>
       <c r="B429" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C429" t="s">
         <v>883</v>
       </c>
       <c r="D429" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E429" t="s">
         <v>10</v>
       </c>
       <c r="F429">
-        <v>285</v>
+        <v>274</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -12074,19 +12086,19 @@
         <v>884</v>
       </c>
       <c r="B430" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C430" t="s">
         <v>885</v>
       </c>
       <c r="D430" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E430" t="s">
         <v>10</v>
       </c>
       <c r="F430">
-        <v>258</v>
+        <v>177</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -12094,7 +12106,7 @@
         <v>886</v>
       </c>
       <c r="B431" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C431" t="s">
         <v>887</v>
@@ -12106,7 +12118,7 @@
         <v>10</v>
       </c>
       <c r="F431">
-        <v>268</v>
+        <v>159</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -12126,7 +12138,7 @@
         <v>10</v>
       </c>
       <c r="F432">
-        <v>242</v>
+        <v>133</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -12146,7 +12158,7 @@
         <v>10</v>
       </c>
       <c r="F433">
-        <v>115</v>
+        <v>259</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -12166,7 +12178,7 @@
         <v>10</v>
       </c>
       <c r="F434">
-        <v>266</v>
+        <v>205</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -12186,7 +12198,7 @@
         <v>10</v>
       </c>
       <c r="F435">
-        <v>182</v>
+        <v>148</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -12206,7 +12218,7 @@
         <v>10</v>
       </c>
       <c r="F436">
-        <v>253</v>
+        <v>160</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -12226,7 +12238,7 @@
         <v>10</v>
       </c>
       <c r="F437">
-        <v>180</v>
+        <v>197</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -12246,7 +12258,7 @@
         <v>10</v>
       </c>
       <c r="F438">
-        <v>289</v>
+        <v>166</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -12266,7 +12278,7 @@
         <v>10</v>
       </c>
       <c r="F439">
-        <v>223</v>
+        <v>174</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -12286,7 +12298,7 @@
         <v>10</v>
       </c>
       <c r="F440">
-        <v>173</v>
+        <v>184</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -12306,7 +12318,7 @@
         <v>10</v>
       </c>
       <c r="F441">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -12326,7 +12338,7 @@
         <v>10</v>
       </c>
       <c r="F442">
-        <v>218</v>
+        <v>272</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -12346,7 +12358,7 @@
         <v>10</v>
       </c>
       <c r="F443">
-        <v>293</v>
+        <v>134</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -12366,7 +12378,7 @@
         <v>10</v>
       </c>
       <c r="F444">
-        <v>113</v>
+        <v>137</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -12386,7 +12398,7 @@
         <v>10</v>
       </c>
       <c r="F445">
-        <v>186</v>
+        <v>229</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -12406,7 +12418,7 @@
         <v>10</v>
       </c>
       <c r="F446">
-        <v>131</v>
+        <v>203</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -12426,7 +12438,7 @@
         <v>10</v>
       </c>
       <c r="F447">
-        <v>181</v>
+        <v>235</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -12446,7 +12458,7 @@
         <v>10</v>
       </c>
       <c r="F448">
-        <v>285</v>
+        <v>195</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -12466,7 +12478,7 @@
         <v>10</v>
       </c>
       <c r="F449">
-        <v>149</v>
+        <v>256</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -12486,7 +12498,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>269</v>
+        <v>145</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -12506,7 +12518,7 @@
         <v>10</v>
       </c>
       <c r="F451">
-        <v>194</v>
+        <v>142</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -12520,13 +12532,13 @@
         <v>931</v>
       </c>
       <c r="D452" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E452" t="s">
         <v>10</v>
       </c>
       <c r="F452">
-        <v>142</v>
+        <v>294</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -12540,13 +12552,13 @@
         <v>933</v>
       </c>
       <c r="D453" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E453" t="s">
         <v>10</v>
       </c>
       <c r="F453">
-        <v>231</v>
+        <v>162</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -12560,13 +12572,13 @@
         <v>935</v>
       </c>
       <c r="D454" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E454" t="s">
         <v>10</v>
       </c>
       <c r="F454">
-        <v>277</v>
+        <v>116</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -12580,13 +12592,13 @@
         <v>937</v>
       </c>
       <c r="D455" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E455" t="s">
         <v>10</v>
       </c>
       <c r="F455">
-        <v>242</v>
+        <v>202</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -12600,13 +12612,13 @@
         <v>939</v>
       </c>
       <c r="D456" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E456" t="s">
         <v>10</v>
       </c>
       <c r="F456">
-        <v>101</v>
+        <v>199</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -12620,13 +12632,13 @@
         <v>941</v>
       </c>
       <c r="D457" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E457" t="s">
         <v>10</v>
       </c>
       <c r="F457">
-        <v>173</v>
+        <v>111</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -12640,13 +12652,13 @@
         <v>943</v>
       </c>
       <c r="D458" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E458" t="s">
         <v>10</v>
       </c>
       <c r="F458">
-        <v>139</v>
+        <v>198</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -12660,13 +12672,13 @@
         <v>945</v>
       </c>
       <c r="D459" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E459" t="s">
         <v>10</v>
       </c>
       <c r="F459">
-        <v>253</v>
+        <v>227</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -12680,13 +12692,13 @@
         <v>947</v>
       </c>
       <c r="D460" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E460" t="s">
         <v>10</v>
       </c>
       <c r="F460">
-        <v>238</v>
+        <v>218</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -12700,13 +12712,13 @@
         <v>949</v>
       </c>
       <c r="D461" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E461" t="s">
         <v>10</v>
       </c>
       <c r="F461">
-        <v>270</v>
+        <v>130</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -12720,13 +12732,13 @@
         <v>951</v>
       </c>
       <c r="D462" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E462" t="s">
         <v>10</v>
       </c>
       <c r="F462">
-        <v>177</v>
+        <v>240</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -12740,13 +12752,13 @@
         <v>953</v>
       </c>
       <c r="D463" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E463" t="s">
         <v>10</v>
       </c>
       <c r="F463">
-        <v>193</v>
+        <v>166</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -12760,13 +12772,13 @@
         <v>955</v>
       </c>
       <c r="D464" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E464" t="s">
         <v>10</v>
       </c>
       <c r="F464">
-        <v>152</v>
+        <v>103</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -12780,13 +12792,13 @@
         <v>957</v>
       </c>
       <c r="D465" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E465" t="s">
         <v>10</v>
       </c>
       <c r="F465">
-        <v>182</v>
+        <v>240</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -12800,13 +12812,13 @@
         <v>959</v>
       </c>
       <c r="D466" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E466" t="s">
         <v>10</v>
       </c>
       <c r="F466">
-        <v>211</v>
+        <v>259</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -12820,13 +12832,13 @@
         <v>961</v>
       </c>
       <c r="D467" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E467" t="s">
         <v>10</v>
       </c>
       <c r="F467">
-        <v>128</v>
+        <v>184</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -12840,13 +12852,13 @@
         <v>963</v>
       </c>
       <c r="D468" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E468" t="s">
         <v>10</v>
       </c>
       <c r="F468">
-        <v>159</v>
+        <v>299</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -12860,13 +12872,13 @@
         <v>965</v>
       </c>
       <c r="D469" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E469" t="s">
         <v>10</v>
       </c>
       <c r="F469">
-        <v>106</v>
+        <v>243</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -12880,13 +12892,13 @@
         <v>967</v>
       </c>
       <c r="D470" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E470" t="s">
         <v>10</v>
       </c>
       <c r="F470">
-        <v>144</v>
+        <v>266</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -12900,13 +12912,13 @@
         <v>969</v>
       </c>
       <c r="D471" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E471" t="s">
         <v>10</v>
       </c>
       <c r="F471">
-        <v>264</v>
+        <v>205</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -12920,13 +12932,13 @@
         <v>971</v>
       </c>
       <c r="D472" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E472" t="s">
         <v>10</v>
       </c>
       <c r="F472">
-        <v>285</v>
+        <v>121</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -12940,13 +12952,13 @@
         <v>973</v>
       </c>
       <c r="D473" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E473" t="s">
         <v>10</v>
       </c>
       <c r="F473">
-        <v>257</v>
+        <v>162</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -12960,13 +12972,13 @@
         <v>975</v>
       </c>
       <c r="D474" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E474" t="s">
         <v>10</v>
       </c>
       <c r="F474">
-        <v>142</v>
+        <v>181</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -12980,13 +12992,13 @@
         <v>977</v>
       </c>
       <c r="D475" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E475" t="s">
         <v>10</v>
       </c>
       <c r="F475">
-        <v>170</v>
+        <v>233</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -13000,13 +13012,13 @@
         <v>979</v>
       </c>
       <c r="D476" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E476" t="s">
         <v>10</v>
       </c>
       <c r="F476">
-        <v>117</v>
+        <v>133</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -13020,13 +13032,13 @@
         <v>981</v>
       </c>
       <c r="D477" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E477" t="s">
         <v>10</v>
       </c>
       <c r="F477">
-        <v>109</v>
+        <v>138</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -13040,13 +13052,13 @@
         <v>983</v>
       </c>
       <c r="D478" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E478" t="s">
         <v>10</v>
       </c>
       <c r="F478">
-        <v>253</v>
+        <v>180</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -13060,13 +13072,13 @@
         <v>985</v>
       </c>
       <c r="D479" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E479" t="s">
         <v>10</v>
       </c>
       <c r="F479">
-        <v>281</v>
+        <v>198</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -13080,13 +13092,13 @@
         <v>987</v>
       </c>
       <c r="D480" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E480" t="s">
         <v>10</v>
       </c>
       <c r="F480">
-        <v>219</v>
+        <v>287</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -13100,13 +13112,13 @@
         <v>989</v>
       </c>
       <c r="D481" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E481" t="s">
         <v>10</v>
       </c>
       <c r="F481">
-        <v>195</v>
+        <v>138</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -13120,13 +13132,13 @@
         <v>991</v>
       </c>
       <c r="D482" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E482" t="s">
         <v>10</v>
       </c>
       <c r="F482">
-        <v>290</v>
+        <v>242</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -13140,13 +13152,13 @@
         <v>993</v>
       </c>
       <c r="D483" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E483" t="s">
         <v>10</v>
       </c>
       <c r="F483">
-        <v>280</v>
+        <v>223</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -13160,13 +13172,13 @@
         <v>995</v>
       </c>
       <c r="D484" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E484" t="s">
         <v>10</v>
       </c>
       <c r="F484">
-        <v>191</v>
+        <v>153</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -13180,13 +13192,13 @@
         <v>997</v>
       </c>
       <c r="D485" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E485" t="s">
         <v>10</v>
       </c>
       <c r="F485">
-        <v>160</v>
+        <v>288</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -13200,13 +13212,13 @@
         <v>999</v>
       </c>
       <c r="D486" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E486" t="s">
         <v>10</v>
       </c>
       <c r="F486">
-        <v>117</v>
+        <v>285</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -13220,13 +13232,13 @@
         <v>1001</v>
       </c>
       <c r="D487" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E487" t="s">
         <v>10</v>
       </c>
       <c r="F487">
-        <v>113</v>
+        <v>145</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -13240,13 +13252,13 @@
         <v>1003</v>
       </c>
       <c r="D488" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E488" t="s">
         <v>10</v>
       </c>
       <c r="F488">
-        <v>129</v>
+        <v>183</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -13260,13 +13272,13 @@
         <v>1005</v>
       </c>
       <c r="D489" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E489" t="s">
         <v>10</v>
       </c>
       <c r="F489">
-        <v>175</v>
+        <v>189</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -13280,13 +13292,13 @@
         <v>1007</v>
       </c>
       <c r="D490" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E490" t="s">
         <v>10</v>
       </c>
       <c r="F490">
-        <v>101</v>
+        <v>270</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -13300,13 +13312,13 @@
         <v>1009</v>
       </c>
       <c r="D491" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E491" t="s">
         <v>10</v>
       </c>
       <c r="F491">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -13320,13 +13332,13 @@
         <v>1011</v>
       </c>
       <c r="D492" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E492" t="s">
         <v>10</v>
       </c>
       <c r="F492">
-        <v>120</v>
+        <v>292</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -13340,13 +13352,13 @@
         <v>1013</v>
       </c>
       <c r="D493" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E493" t="s">
         <v>10</v>
       </c>
       <c r="F493">
-        <v>185</v>
+        <v>297</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -13360,13 +13372,13 @@
         <v>1015</v>
       </c>
       <c r="D494" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E494" t="s">
         <v>10</v>
       </c>
       <c r="F494">
-        <v>235</v>
+        <v>189</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -13380,13 +13392,13 @@
         <v>1017</v>
       </c>
       <c r="D495" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E495" t="s">
         <v>10</v>
       </c>
       <c r="F495">
-        <v>260</v>
+        <v>101</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -13400,13 +13412,13 @@
         <v>1019</v>
       </c>
       <c r="D496" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E496" t="s">
         <v>10</v>
       </c>
       <c r="F496">
-        <v>228</v>
+        <v>240</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -13420,13 +13432,13 @@
         <v>1021</v>
       </c>
       <c r="D497" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E497" t="s">
         <v>10</v>
       </c>
       <c r="F497">
-        <v>169</v>
+        <v>111</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -13440,13 +13452,13 @@
         <v>1023</v>
       </c>
       <c r="D498" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E498" t="s">
         <v>10</v>
       </c>
       <c r="F498">
-        <v>219</v>
+        <v>138</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -13460,13 +13472,53 @@
         <v>1025</v>
       </c>
       <c r="D499" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E499" t="s">
         <v>10</v>
       </c>
       <c r="F499">
-        <v>194</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B500" t="s">
+        <v>930</v>
+      </c>
+      <c r="C500" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D500" t="s">
+        <v>9</v>
+      </c>
+      <c r="E500" t="s">
+        <v>10</v>
+      </c>
+      <c r="F500">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B501" t="s">
+        <v>930</v>
+      </c>
+      <c r="C501" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D501" t="s">
+        <v>13</v>
+      </c>
+      <c r="E501" t="s">
+        <v>10</v>
+      </c>
+      <c r="F501">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
